--- a/NV Play Women's Fixtures player appearances for abandoned games.xlsx
+++ b/NV Play Women's Fixtures player appearances for abandoned games.xlsx
@@ -1,178 +1,166 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24510" windowHeight="14280"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="24510" windowHeight="14280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NV Play batting stats for seaso" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NV Play batting stats for seaso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Matches</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="19">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="Calibri Light"/>
       <family val="2"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -219,19 +207,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -242,19 +230,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -265,19 +253,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -288,19 +276,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -311,19 +299,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -334,20 +322,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -382,7 +376,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </bottom>
       <diagonal/>
     </border>
@@ -468,107 +462,167 @@
     </border>
   </borders>
   <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
+    <cellStyle name="Good" xfId="6" builtinId="26"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
+    <cellStyle name="Input" xfId="9" builtinId="20"/>
+    <cellStyle name="Output" xfId="10" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="Note" xfId="15" builtinId="10"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
+    <cellStyle name="Total" xfId="17" builtinId="25"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -834,124 +888,4927 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C4890"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="63.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col width="10" customWidth="1" style="1" min="1" max="1"/>
+    <col width="10" customWidth="1" style="1" min="2" max="2"/>
+    <col width="10" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Matches</t>
+        </is>
       </c>
     </row>
-    <row r="4859" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4859" s="1"/>
-    </row>
-    <row r="4860" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4860" s="1"/>
-    </row>
-    <row r="4861" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4861" s="1"/>
-    </row>
-    <row r="4862" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4862" s="1"/>
-    </row>
-    <row r="4863" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4863" s="1"/>
-    </row>
-    <row r="4864" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4864" s="1"/>
-    </row>
-    <row r="4865" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4865" s="1"/>
-    </row>
-    <row r="4866" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4866" s="1"/>
-    </row>
-    <row r="4867" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4867" s="1"/>
-    </row>
-    <row r="4868" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4868" s="1"/>
-    </row>
-    <row r="4869" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4869" s="1"/>
-    </row>
-    <row r="4870" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4870" s="1"/>
-    </row>
-    <row r="4871" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4871" s="1"/>
-    </row>
-    <row r="4872" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4872" s="1"/>
-    </row>
-    <row r="4873" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4873" s="1"/>
-    </row>
-    <row r="4874" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4874" s="1"/>
-    </row>
-    <row r="4875" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4875" s="1"/>
-    </row>
-    <row r="4876" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4876" s="1"/>
-    </row>
-    <row r="4877" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4877" s="1"/>
-    </row>
-    <row r="4878" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4878" s="1"/>
-    </row>
-    <row r="4879" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4879" s="1"/>
-    </row>
-    <row r="4880" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4880" s="1"/>
-    </row>
-    <row r="4881" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4881" s="1"/>
-    </row>
-    <row r="4882" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4882" s="1"/>
-    </row>
-    <row r="4883" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4883" s="1"/>
-    </row>
-    <row r="4884" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4884" s="1"/>
-    </row>
-    <row r="4885" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4885" s="1"/>
-    </row>
-    <row r="4886" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4886" s="1"/>
-    </row>
-    <row r="4887" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4887" s="1"/>
-    </row>
-    <row r="4888" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4888" s="1"/>
-    </row>
-    <row r="4889" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4889" s="1"/>
-    </row>
-    <row r="4890" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4890" s="1"/>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220"/>
+    <row r="1221"/>
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248"/>
+    <row r="1249"/>
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293"/>
+    <row r="1294"/>
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321"/>
+    <row r="1322"/>
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349"/>
+    <row r="1350"/>
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377"/>
+    <row r="1378"/>
+    <row r="1379"/>
+    <row r="1380"/>
+    <row r="1381"/>
+    <row r="1382"/>
+    <row r="1383"/>
+    <row r="1384"/>
+    <row r="1385"/>
+    <row r="1386"/>
+    <row r="1387"/>
+    <row r="1388"/>
+    <row r="1389"/>
+    <row r="1390"/>
+    <row r="1391"/>
+    <row r="1392"/>
+    <row r="1393"/>
+    <row r="1394"/>
+    <row r="1395"/>
+    <row r="1396"/>
+    <row r="1397"/>
+    <row r="1398"/>
+    <row r="1399"/>
+    <row r="1400"/>
+    <row r="1401"/>
+    <row r="1402"/>
+    <row r="1403"/>
+    <row r="1404"/>
+    <row r="1405"/>
+    <row r="1406"/>
+    <row r="1407"/>
+    <row r="1408"/>
+    <row r="1409"/>
+    <row r="1410"/>
+    <row r="1411"/>
+    <row r="1412"/>
+    <row r="1413"/>
+    <row r="1414"/>
+    <row r="1415"/>
+    <row r="1416"/>
+    <row r="1417"/>
+    <row r="1418"/>
+    <row r="1419"/>
+    <row r="1420"/>
+    <row r="1421"/>
+    <row r="1422"/>
+    <row r="1423"/>
+    <row r="1424"/>
+    <row r="1425"/>
+    <row r="1426"/>
+    <row r="1427"/>
+    <row r="1428"/>
+    <row r="1429"/>
+    <row r="1430"/>
+    <row r="1431"/>
+    <row r="1432"/>
+    <row r="1433"/>
+    <row r="1434"/>
+    <row r="1435"/>
+    <row r="1436"/>
+    <row r="1437"/>
+    <row r="1438"/>
+    <row r="1439"/>
+    <row r="1440"/>
+    <row r="1441"/>
+    <row r="1442"/>
+    <row r="1443"/>
+    <row r="1444"/>
+    <row r="1445"/>
+    <row r="1446"/>
+    <row r="1447"/>
+    <row r="1448"/>
+    <row r="1449"/>
+    <row r="1450"/>
+    <row r="1451"/>
+    <row r="1452"/>
+    <row r="1453"/>
+    <row r="1454"/>
+    <row r="1455"/>
+    <row r="1456"/>
+    <row r="1457"/>
+    <row r="1458"/>
+    <row r="1459"/>
+    <row r="1460"/>
+    <row r="1461"/>
+    <row r="1462"/>
+    <row r="1463"/>
+    <row r="1464"/>
+    <row r="1465"/>
+    <row r="1466"/>
+    <row r="1467"/>
+    <row r="1468"/>
+    <row r="1469"/>
+    <row r="1470"/>
+    <row r="1471"/>
+    <row r="1472"/>
+    <row r="1473"/>
+    <row r="1474"/>
+    <row r="1475"/>
+    <row r="1476"/>
+    <row r="1477"/>
+    <row r="1478"/>
+    <row r="1479"/>
+    <row r="1480"/>
+    <row r="1481"/>
+    <row r="1482"/>
+    <row r="1483"/>
+    <row r="1484"/>
+    <row r="1485"/>
+    <row r="1486"/>
+    <row r="1487"/>
+    <row r="1488"/>
+    <row r="1489"/>
+    <row r="1490"/>
+    <row r="1491"/>
+    <row r="1492"/>
+    <row r="1493"/>
+    <row r="1494"/>
+    <row r="1495"/>
+    <row r="1496"/>
+    <row r="1497"/>
+    <row r="1498"/>
+    <row r="1499"/>
+    <row r="1500"/>
+    <row r="1501"/>
+    <row r="1502"/>
+    <row r="1503"/>
+    <row r="1504"/>
+    <row r="1505"/>
+    <row r="1506"/>
+    <row r="1507"/>
+    <row r="1508"/>
+    <row r="1509"/>
+    <row r="1510"/>
+    <row r="1511"/>
+    <row r="1512"/>
+    <row r="1513"/>
+    <row r="1514"/>
+    <row r="1515"/>
+    <row r="1516"/>
+    <row r="1517"/>
+    <row r="1518"/>
+    <row r="1519"/>
+    <row r="1520"/>
+    <row r="1521"/>
+    <row r="1522"/>
+    <row r="1523"/>
+    <row r="1524"/>
+    <row r="1525"/>
+    <row r="1526"/>
+    <row r="1527"/>
+    <row r="1528"/>
+    <row r="1529"/>
+    <row r="1530"/>
+    <row r="1531"/>
+    <row r="1532"/>
+    <row r="1533"/>
+    <row r="1534"/>
+    <row r="1535"/>
+    <row r="1536"/>
+    <row r="1537"/>
+    <row r="1538"/>
+    <row r="1539"/>
+    <row r="1540"/>
+    <row r="1541"/>
+    <row r="1542"/>
+    <row r="1543"/>
+    <row r="1544"/>
+    <row r="1545"/>
+    <row r="1546"/>
+    <row r="1547"/>
+    <row r="1548"/>
+    <row r="1549"/>
+    <row r="1550"/>
+    <row r="1551"/>
+    <row r="1552"/>
+    <row r="1553"/>
+    <row r="1554"/>
+    <row r="1555"/>
+    <row r="1556"/>
+    <row r="1557"/>
+    <row r="1558"/>
+    <row r="1559"/>
+    <row r="1560"/>
+    <row r="1561"/>
+    <row r="1562"/>
+    <row r="1563"/>
+    <row r="1564"/>
+    <row r="1565"/>
+    <row r="1566"/>
+    <row r="1567"/>
+    <row r="1568"/>
+    <row r="1569"/>
+    <row r="1570"/>
+    <row r="1571"/>
+    <row r="1572"/>
+    <row r="1573"/>
+    <row r="1574"/>
+    <row r="1575"/>
+    <row r="1576"/>
+    <row r="1577"/>
+    <row r="1578"/>
+    <row r="1579"/>
+    <row r="1580"/>
+    <row r="1581"/>
+    <row r="1582"/>
+    <row r="1583"/>
+    <row r="1584"/>
+    <row r="1585"/>
+    <row r="1586"/>
+    <row r="1587"/>
+    <row r="1588"/>
+    <row r="1589"/>
+    <row r="1590"/>
+    <row r="1591"/>
+    <row r="1592"/>
+    <row r="1593"/>
+    <row r="1594"/>
+    <row r="1595"/>
+    <row r="1596"/>
+    <row r="1597"/>
+    <row r="1598"/>
+    <row r="1599"/>
+    <row r="1600"/>
+    <row r="1601"/>
+    <row r="1602"/>
+    <row r="1603"/>
+    <row r="1604"/>
+    <row r="1605"/>
+    <row r="1606"/>
+    <row r="1607"/>
+    <row r="1608"/>
+    <row r="1609"/>
+    <row r="1610"/>
+    <row r="1611"/>
+    <row r="1612"/>
+    <row r="1613"/>
+    <row r="1614"/>
+    <row r="1615"/>
+    <row r="1616"/>
+    <row r="1617"/>
+    <row r="1618"/>
+    <row r="1619"/>
+    <row r="1620"/>
+    <row r="1621"/>
+    <row r="1622"/>
+    <row r="1623"/>
+    <row r="1624"/>
+    <row r="1625"/>
+    <row r="1626"/>
+    <row r="1627"/>
+    <row r="1628"/>
+    <row r="1629"/>
+    <row r="1630"/>
+    <row r="1631"/>
+    <row r="1632"/>
+    <row r="1633"/>
+    <row r="1634"/>
+    <row r="1635"/>
+    <row r="1636"/>
+    <row r="1637"/>
+    <row r="1638"/>
+    <row r="1639"/>
+    <row r="1640"/>
+    <row r="1641"/>
+    <row r="1642"/>
+    <row r="1643"/>
+    <row r="1644"/>
+    <row r="1645"/>
+    <row r="1646"/>
+    <row r="1647"/>
+    <row r="1648"/>
+    <row r="1649"/>
+    <row r="1650"/>
+    <row r="1651"/>
+    <row r="1652"/>
+    <row r="1653"/>
+    <row r="1654"/>
+    <row r="1655"/>
+    <row r="1656"/>
+    <row r="1657"/>
+    <row r="1658"/>
+    <row r="1659"/>
+    <row r="1660"/>
+    <row r="1661"/>
+    <row r="1662"/>
+    <row r="1663"/>
+    <row r="1664"/>
+    <row r="1665"/>
+    <row r="1666"/>
+    <row r="1667"/>
+    <row r="1668"/>
+    <row r="1669"/>
+    <row r="1670"/>
+    <row r="1671"/>
+    <row r="1672"/>
+    <row r="1673"/>
+    <row r="1674"/>
+    <row r="1675"/>
+    <row r="1676"/>
+    <row r="1677"/>
+    <row r="1678"/>
+    <row r="1679"/>
+    <row r="1680"/>
+    <row r="1681"/>
+    <row r="1682"/>
+    <row r="1683"/>
+    <row r="1684"/>
+    <row r="1685"/>
+    <row r="1686"/>
+    <row r="1687"/>
+    <row r="1688"/>
+    <row r="1689"/>
+    <row r="1690"/>
+    <row r="1691"/>
+    <row r="1692"/>
+    <row r="1693"/>
+    <row r="1694"/>
+    <row r="1695"/>
+    <row r="1696"/>
+    <row r="1697"/>
+    <row r="1698"/>
+    <row r="1699"/>
+    <row r="1700"/>
+    <row r="1701"/>
+    <row r="1702"/>
+    <row r="1703"/>
+    <row r="1704"/>
+    <row r="1705"/>
+    <row r="1706"/>
+    <row r="1707"/>
+    <row r="1708"/>
+    <row r="1709"/>
+    <row r="1710"/>
+    <row r="1711"/>
+    <row r="1712"/>
+    <row r="1713"/>
+    <row r="1714"/>
+    <row r="1715"/>
+    <row r="1716"/>
+    <row r="1717"/>
+    <row r="1718"/>
+    <row r="1719"/>
+    <row r="1720"/>
+    <row r="1721"/>
+    <row r="1722"/>
+    <row r="1723"/>
+    <row r="1724"/>
+    <row r="1725"/>
+    <row r="1726"/>
+    <row r="1727"/>
+    <row r="1728"/>
+    <row r="1729"/>
+    <row r="1730"/>
+    <row r="1731"/>
+    <row r="1732"/>
+    <row r="1733"/>
+    <row r="1734"/>
+    <row r="1735"/>
+    <row r="1736"/>
+    <row r="1737"/>
+    <row r="1738"/>
+    <row r="1739"/>
+    <row r="1740"/>
+    <row r="1741"/>
+    <row r="1742"/>
+    <row r="1743"/>
+    <row r="1744"/>
+    <row r="1745"/>
+    <row r="1746"/>
+    <row r="1747"/>
+    <row r="1748"/>
+    <row r="1749"/>
+    <row r="1750"/>
+    <row r="1751"/>
+    <row r="1752"/>
+    <row r="1753"/>
+    <row r="1754"/>
+    <row r="1755"/>
+    <row r="1756"/>
+    <row r="1757"/>
+    <row r="1758"/>
+    <row r="1759"/>
+    <row r="1760"/>
+    <row r="1761"/>
+    <row r="1762"/>
+    <row r="1763"/>
+    <row r="1764"/>
+    <row r="1765"/>
+    <row r="1766"/>
+    <row r="1767"/>
+    <row r="1768"/>
+    <row r="1769"/>
+    <row r="1770"/>
+    <row r="1771"/>
+    <row r="1772"/>
+    <row r="1773"/>
+    <row r="1774"/>
+    <row r="1775"/>
+    <row r="1776"/>
+    <row r="1777"/>
+    <row r="1778"/>
+    <row r="1779"/>
+    <row r="1780"/>
+    <row r="1781"/>
+    <row r="1782"/>
+    <row r="1783"/>
+    <row r="1784"/>
+    <row r="1785"/>
+    <row r="1786"/>
+    <row r="1787"/>
+    <row r="1788"/>
+    <row r="1789"/>
+    <row r="1790"/>
+    <row r="1791"/>
+    <row r="1792"/>
+    <row r="1793"/>
+    <row r="1794"/>
+    <row r="1795"/>
+    <row r="1796"/>
+    <row r="1797"/>
+    <row r="1798"/>
+    <row r="1799"/>
+    <row r="1800"/>
+    <row r="1801"/>
+    <row r="1802"/>
+    <row r="1803"/>
+    <row r="1804"/>
+    <row r="1805"/>
+    <row r="1806"/>
+    <row r="1807"/>
+    <row r="1808"/>
+    <row r="1809"/>
+    <row r="1810"/>
+    <row r="1811"/>
+    <row r="1812"/>
+    <row r="1813"/>
+    <row r="1814"/>
+    <row r="1815"/>
+    <row r="1816"/>
+    <row r="1817"/>
+    <row r="1818"/>
+    <row r="1819"/>
+    <row r="1820"/>
+    <row r="1821"/>
+    <row r="1822"/>
+    <row r="1823"/>
+    <row r="1824"/>
+    <row r="1825"/>
+    <row r="1826"/>
+    <row r="1827"/>
+    <row r="1828"/>
+    <row r="1829"/>
+    <row r="1830"/>
+    <row r="1831"/>
+    <row r="1832"/>
+    <row r="1833"/>
+    <row r="1834"/>
+    <row r="1835"/>
+    <row r="1836"/>
+    <row r="1837"/>
+    <row r="1838"/>
+    <row r="1839"/>
+    <row r="1840"/>
+    <row r="1841"/>
+    <row r="1842"/>
+    <row r="1843"/>
+    <row r="1844"/>
+    <row r="1845"/>
+    <row r="1846"/>
+    <row r="1847"/>
+    <row r="1848"/>
+    <row r="1849"/>
+    <row r="1850"/>
+    <row r="1851"/>
+    <row r="1852"/>
+    <row r="1853"/>
+    <row r="1854"/>
+    <row r="1855"/>
+    <row r="1856"/>
+    <row r="1857"/>
+    <row r="1858"/>
+    <row r="1859"/>
+    <row r="1860"/>
+    <row r="1861"/>
+    <row r="1862"/>
+    <row r="1863"/>
+    <row r="1864"/>
+    <row r="1865"/>
+    <row r="1866"/>
+    <row r="1867"/>
+    <row r="1868"/>
+    <row r="1869"/>
+    <row r="1870"/>
+    <row r="1871"/>
+    <row r="1872"/>
+    <row r="1873"/>
+    <row r="1874"/>
+    <row r="1875"/>
+    <row r="1876"/>
+    <row r="1877"/>
+    <row r="1878"/>
+    <row r="1879"/>
+    <row r="1880"/>
+    <row r="1881"/>
+    <row r="1882"/>
+    <row r="1883"/>
+    <row r="1884"/>
+    <row r="1885"/>
+    <row r="1886"/>
+    <row r="1887"/>
+    <row r="1888"/>
+    <row r="1889"/>
+    <row r="1890"/>
+    <row r="1891"/>
+    <row r="1892"/>
+    <row r="1893"/>
+    <row r="1894"/>
+    <row r="1895"/>
+    <row r="1896"/>
+    <row r="1897"/>
+    <row r="1898"/>
+    <row r="1899"/>
+    <row r="1900"/>
+    <row r="1901"/>
+    <row r="1902"/>
+    <row r="1903"/>
+    <row r="1904"/>
+    <row r="1905"/>
+    <row r="1906"/>
+    <row r="1907"/>
+    <row r="1908"/>
+    <row r="1909"/>
+    <row r="1910"/>
+    <row r="1911"/>
+    <row r="1912"/>
+    <row r="1913"/>
+    <row r="1914"/>
+    <row r="1915"/>
+    <row r="1916"/>
+    <row r="1917"/>
+    <row r="1918"/>
+    <row r="1919"/>
+    <row r="1920"/>
+    <row r="1921"/>
+    <row r="1922"/>
+    <row r="1923"/>
+    <row r="1924"/>
+    <row r="1925"/>
+    <row r="1926"/>
+    <row r="1927"/>
+    <row r="1928"/>
+    <row r="1929"/>
+    <row r="1930"/>
+    <row r="1931"/>
+    <row r="1932"/>
+    <row r="1933"/>
+    <row r="1934"/>
+    <row r="1935"/>
+    <row r="1936"/>
+    <row r="1937"/>
+    <row r="1938"/>
+    <row r="1939"/>
+    <row r="1940"/>
+    <row r="1941"/>
+    <row r="1942"/>
+    <row r="1943"/>
+    <row r="1944"/>
+    <row r="1945"/>
+    <row r="1946"/>
+    <row r="1947"/>
+    <row r="1948"/>
+    <row r="1949"/>
+    <row r="1950"/>
+    <row r="1951"/>
+    <row r="1952"/>
+    <row r="1953"/>
+    <row r="1954"/>
+    <row r="1955"/>
+    <row r="1956"/>
+    <row r="1957"/>
+    <row r="1958"/>
+    <row r="1959"/>
+    <row r="1960"/>
+    <row r="1961"/>
+    <row r="1962"/>
+    <row r="1963"/>
+    <row r="1964"/>
+    <row r="1965"/>
+    <row r="1966"/>
+    <row r="1967"/>
+    <row r="1968"/>
+    <row r="1969"/>
+    <row r="1970"/>
+    <row r="1971"/>
+    <row r="1972"/>
+    <row r="1973"/>
+    <row r="1974"/>
+    <row r="1975"/>
+    <row r="1976"/>
+    <row r="1977"/>
+    <row r="1978"/>
+    <row r="1979"/>
+    <row r="1980"/>
+    <row r="1981"/>
+    <row r="1982"/>
+    <row r="1983"/>
+    <row r="1984"/>
+    <row r="1985"/>
+    <row r="1986"/>
+    <row r="1987"/>
+    <row r="1988"/>
+    <row r="1989"/>
+    <row r="1990"/>
+    <row r="1991"/>
+    <row r="1992"/>
+    <row r="1993"/>
+    <row r="1994"/>
+    <row r="1995"/>
+    <row r="1996"/>
+    <row r="1997"/>
+    <row r="1998"/>
+    <row r="1999"/>
+    <row r="2000"/>
+    <row r="2001"/>
+    <row r="2002"/>
+    <row r="2003"/>
+    <row r="2004"/>
+    <row r="2005"/>
+    <row r="2006"/>
+    <row r="2007"/>
+    <row r="2008"/>
+    <row r="2009"/>
+    <row r="2010"/>
+    <row r="2011"/>
+    <row r="2012"/>
+    <row r="2013"/>
+    <row r="2014"/>
+    <row r="2015"/>
+    <row r="2016"/>
+    <row r="2017"/>
+    <row r="2018"/>
+    <row r="2019"/>
+    <row r="2020"/>
+    <row r="2021"/>
+    <row r="2022"/>
+    <row r="2023"/>
+    <row r="2024"/>
+    <row r="2025"/>
+    <row r="2026"/>
+    <row r="2027"/>
+    <row r="2028"/>
+    <row r="2029"/>
+    <row r="2030"/>
+    <row r="2031"/>
+    <row r="2032"/>
+    <row r="2033"/>
+    <row r="2034"/>
+    <row r="2035"/>
+    <row r="2036"/>
+    <row r="2037"/>
+    <row r="2038"/>
+    <row r="2039"/>
+    <row r="2040"/>
+    <row r="2041"/>
+    <row r="2042"/>
+    <row r="2043"/>
+    <row r="2044"/>
+    <row r="2045"/>
+    <row r="2046"/>
+    <row r="2047"/>
+    <row r="2048"/>
+    <row r="2049"/>
+    <row r="2050"/>
+    <row r="2051"/>
+    <row r="2052"/>
+    <row r="2053"/>
+    <row r="2054"/>
+    <row r="2055"/>
+    <row r="2056"/>
+    <row r="2057"/>
+    <row r="2058"/>
+    <row r="2059"/>
+    <row r="2060"/>
+    <row r="2061"/>
+    <row r="2062"/>
+    <row r="2063"/>
+    <row r="2064"/>
+    <row r="2065"/>
+    <row r="2066"/>
+    <row r="2067"/>
+    <row r="2068"/>
+    <row r="2069"/>
+    <row r="2070"/>
+    <row r="2071"/>
+    <row r="2072"/>
+    <row r="2073"/>
+    <row r="2074"/>
+    <row r="2075"/>
+    <row r="2076"/>
+    <row r="2077"/>
+    <row r="2078"/>
+    <row r="2079"/>
+    <row r="2080"/>
+    <row r="2081"/>
+    <row r="2082"/>
+    <row r="2083"/>
+    <row r="2084"/>
+    <row r="2085"/>
+    <row r="2086"/>
+    <row r="2087"/>
+    <row r="2088"/>
+    <row r="2089"/>
+    <row r="2090"/>
+    <row r="2091"/>
+    <row r="2092"/>
+    <row r="2093"/>
+    <row r="2094"/>
+    <row r="2095"/>
+    <row r="2096"/>
+    <row r="2097"/>
+    <row r="2098"/>
+    <row r="2099"/>
+    <row r="2100"/>
+    <row r="2101"/>
+    <row r="2102"/>
+    <row r="2103"/>
+    <row r="2104"/>
+    <row r="2105"/>
+    <row r="2106"/>
+    <row r="2107"/>
+    <row r="2108"/>
+    <row r="2109"/>
+    <row r="2110"/>
+    <row r="2111"/>
+    <row r="2112"/>
+    <row r="2113"/>
+    <row r="2114"/>
+    <row r="2115"/>
+    <row r="2116"/>
+    <row r="2117"/>
+    <row r="2118"/>
+    <row r="2119"/>
+    <row r="2120"/>
+    <row r="2121"/>
+    <row r="2122"/>
+    <row r="2123"/>
+    <row r="2124"/>
+    <row r="2125"/>
+    <row r="2126"/>
+    <row r="2127"/>
+    <row r="2128"/>
+    <row r="2129"/>
+    <row r="2130"/>
+    <row r="2131"/>
+    <row r="2132"/>
+    <row r="2133"/>
+    <row r="2134"/>
+    <row r="2135"/>
+    <row r="2136"/>
+    <row r="2137"/>
+    <row r="2138"/>
+    <row r="2139"/>
+    <row r="2140"/>
+    <row r="2141"/>
+    <row r="2142"/>
+    <row r="2143"/>
+    <row r="2144"/>
+    <row r="2145"/>
+    <row r="2146"/>
+    <row r="2147"/>
+    <row r="2148"/>
+    <row r="2149"/>
+    <row r="2150"/>
+    <row r="2151"/>
+    <row r="2152"/>
+    <row r="2153"/>
+    <row r="2154"/>
+    <row r="2155"/>
+    <row r="2156"/>
+    <row r="2157"/>
+    <row r="2158"/>
+    <row r="2159"/>
+    <row r="2160"/>
+    <row r="2161"/>
+    <row r="2162"/>
+    <row r="2163"/>
+    <row r="2164"/>
+    <row r="2165"/>
+    <row r="2166"/>
+    <row r="2167"/>
+    <row r="2168"/>
+    <row r="2169"/>
+    <row r="2170"/>
+    <row r="2171"/>
+    <row r="2172"/>
+    <row r="2173"/>
+    <row r="2174"/>
+    <row r="2175"/>
+    <row r="2176"/>
+    <row r="2177"/>
+    <row r="2178"/>
+    <row r="2179"/>
+    <row r="2180"/>
+    <row r="2181"/>
+    <row r="2182"/>
+    <row r="2183"/>
+    <row r="2184"/>
+    <row r="2185"/>
+    <row r="2186"/>
+    <row r="2187"/>
+    <row r="2188"/>
+    <row r="2189"/>
+    <row r="2190"/>
+    <row r="2191"/>
+    <row r="2192"/>
+    <row r="2193"/>
+    <row r="2194"/>
+    <row r="2195"/>
+    <row r="2196"/>
+    <row r="2197"/>
+    <row r="2198"/>
+    <row r="2199"/>
+    <row r="2200"/>
+    <row r="2201"/>
+    <row r="2202"/>
+    <row r="2203"/>
+    <row r="2204"/>
+    <row r="2205"/>
+    <row r="2206"/>
+    <row r="2207"/>
+    <row r="2208"/>
+    <row r="2209"/>
+    <row r="2210"/>
+    <row r="2211"/>
+    <row r="2212"/>
+    <row r="2213"/>
+    <row r="2214"/>
+    <row r="2215"/>
+    <row r="2216"/>
+    <row r="2217"/>
+    <row r="2218"/>
+    <row r="2219"/>
+    <row r="2220"/>
+    <row r="2221"/>
+    <row r="2222"/>
+    <row r="2223"/>
+    <row r="2224"/>
+    <row r="2225"/>
+    <row r="2226"/>
+    <row r="2227"/>
+    <row r="2228"/>
+    <row r="2229"/>
+    <row r="2230"/>
+    <row r="2231"/>
+    <row r="2232"/>
+    <row r="2233"/>
+    <row r="2234"/>
+    <row r="2235"/>
+    <row r="2236"/>
+    <row r="2237"/>
+    <row r="2238"/>
+    <row r="2239"/>
+    <row r="2240"/>
+    <row r="2241"/>
+    <row r="2242"/>
+    <row r="2243"/>
+    <row r="2244"/>
+    <row r="2245"/>
+    <row r="2246"/>
+    <row r="2247"/>
+    <row r="2248"/>
+    <row r="2249"/>
+    <row r="2250"/>
+    <row r="2251"/>
+    <row r="2252"/>
+    <row r="2253"/>
+    <row r="2254"/>
+    <row r="2255"/>
+    <row r="2256"/>
+    <row r="2257"/>
+    <row r="2258"/>
+    <row r="2259"/>
+    <row r="2260"/>
+    <row r="2261"/>
+    <row r="2262"/>
+    <row r="2263"/>
+    <row r="2264"/>
+    <row r="2265"/>
+    <row r="2266"/>
+    <row r="2267"/>
+    <row r="2268"/>
+    <row r="2269"/>
+    <row r="2270"/>
+    <row r="2271"/>
+    <row r="2272"/>
+    <row r="2273"/>
+    <row r="2274"/>
+    <row r="2275"/>
+    <row r="2276"/>
+    <row r="2277"/>
+    <row r="2278"/>
+    <row r="2279"/>
+    <row r="2280"/>
+    <row r="2281"/>
+    <row r="2282"/>
+    <row r="2283"/>
+    <row r="2284"/>
+    <row r="2285"/>
+    <row r="2286"/>
+    <row r="2287"/>
+    <row r="2288"/>
+    <row r="2289"/>
+    <row r="2290"/>
+    <row r="2291"/>
+    <row r="2292"/>
+    <row r="2293"/>
+    <row r="2294"/>
+    <row r="2295"/>
+    <row r="2296"/>
+    <row r="2297"/>
+    <row r="2298"/>
+    <row r="2299"/>
+    <row r="2300"/>
+    <row r="2301"/>
+    <row r="2302"/>
+    <row r="2303"/>
+    <row r="2304"/>
+    <row r="2305"/>
+    <row r="2306"/>
+    <row r="2307"/>
+    <row r="2308"/>
+    <row r="2309"/>
+    <row r="2310"/>
+    <row r="2311"/>
+    <row r="2312"/>
+    <row r="2313"/>
+    <row r="2314"/>
+    <row r="2315"/>
+    <row r="2316"/>
+    <row r="2317"/>
+    <row r="2318"/>
+    <row r="2319"/>
+    <row r="2320"/>
+    <row r="2321"/>
+    <row r="2322"/>
+    <row r="2323"/>
+    <row r="2324"/>
+    <row r="2325"/>
+    <row r="2326"/>
+    <row r="2327"/>
+    <row r="2328"/>
+    <row r="2329"/>
+    <row r="2330"/>
+    <row r="2331"/>
+    <row r="2332"/>
+    <row r="2333"/>
+    <row r="2334"/>
+    <row r="2335"/>
+    <row r="2336"/>
+    <row r="2337"/>
+    <row r="2338"/>
+    <row r="2339"/>
+    <row r="2340"/>
+    <row r="2341"/>
+    <row r="2342"/>
+    <row r="2343"/>
+    <row r="2344"/>
+    <row r="2345"/>
+    <row r="2346"/>
+    <row r="2347"/>
+    <row r="2348"/>
+    <row r="2349"/>
+    <row r="2350"/>
+    <row r="2351"/>
+    <row r="2352"/>
+    <row r="2353"/>
+    <row r="2354"/>
+    <row r="2355"/>
+    <row r="2356"/>
+    <row r="2357"/>
+    <row r="2358"/>
+    <row r="2359"/>
+    <row r="2360"/>
+    <row r="2361"/>
+    <row r="2362"/>
+    <row r="2363"/>
+    <row r="2364"/>
+    <row r="2365"/>
+    <row r="2366"/>
+    <row r="2367"/>
+    <row r="2368"/>
+    <row r="2369"/>
+    <row r="2370"/>
+    <row r="2371"/>
+    <row r="2372"/>
+    <row r="2373"/>
+    <row r="2374"/>
+    <row r="2375"/>
+    <row r="2376"/>
+    <row r="2377"/>
+    <row r="2378"/>
+    <row r="2379"/>
+    <row r="2380"/>
+    <row r="2381"/>
+    <row r="2382"/>
+    <row r="2383"/>
+    <row r="2384"/>
+    <row r="2385"/>
+    <row r="2386"/>
+    <row r="2387"/>
+    <row r="2388"/>
+    <row r="2389"/>
+    <row r="2390"/>
+    <row r="2391"/>
+    <row r="2392"/>
+    <row r="2393"/>
+    <row r="2394"/>
+    <row r="2395"/>
+    <row r="2396"/>
+    <row r="2397"/>
+    <row r="2398"/>
+    <row r="2399"/>
+    <row r="2400"/>
+    <row r="2401"/>
+    <row r="2402"/>
+    <row r="2403"/>
+    <row r="2404"/>
+    <row r="2405"/>
+    <row r="2406"/>
+    <row r="2407"/>
+    <row r="2408"/>
+    <row r="2409"/>
+    <row r="2410"/>
+    <row r="2411"/>
+    <row r="2412"/>
+    <row r="2413"/>
+    <row r="2414"/>
+    <row r="2415"/>
+    <row r="2416"/>
+    <row r="2417"/>
+    <row r="2418"/>
+    <row r="2419"/>
+    <row r="2420"/>
+    <row r="2421"/>
+    <row r="2422"/>
+    <row r="2423"/>
+    <row r="2424"/>
+    <row r="2425"/>
+    <row r="2426"/>
+    <row r="2427"/>
+    <row r="2428"/>
+    <row r="2429"/>
+    <row r="2430"/>
+    <row r="2431"/>
+    <row r="2432"/>
+    <row r="2433"/>
+    <row r="2434"/>
+    <row r="2435"/>
+    <row r="2436"/>
+    <row r="2437"/>
+    <row r="2438"/>
+    <row r="2439"/>
+    <row r="2440"/>
+    <row r="2441"/>
+    <row r="2442"/>
+    <row r="2443"/>
+    <row r="2444"/>
+    <row r="2445"/>
+    <row r="2446"/>
+    <row r="2447"/>
+    <row r="2448"/>
+    <row r="2449"/>
+    <row r="2450"/>
+    <row r="2451"/>
+    <row r="2452"/>
+    <row r="2453"/>
+    <row r="2454"/>
+    <row r="2455"/>
+    <row r="2456"/>
+    <row r="2457"/>
+    <row r="2458"/>
+    <row r="2459"/>
+    <row r="2460"/>
+    <row r="2461"/>
+    <row r="2462"/>
+    <row r="2463"/>
+    <row r="2464"/>
+    <row r="2465"/>
+    <row r="2466"/>
+    <row r="2467"/>
+    <row r="2468"/>
+    <row r="2469"/>
+    <row r="2470"/>
+    <row r="2471"/>
+    <row r="2472"/>
+    <row r="2473"/>
+    <row r="2474"/>
+    <row r="2475"/>
+    <row r="2476"/>
+    <row r="2477"/>
+    <row r="2478"/>
+    <row r="2479"/>
+    <row r="2480"/>
+    <row r="2481"/>
+    <row r="2482"/>
+    <row r="2483"/>
+    <row r="2484"/>
+    <row r="2485"/>
+    <row r="2486"/>
+    <row r="2487"/>
+    <row r="2488"/>
+    <row r="2489"/>
+    <row r="2490"/>
+    <row r="2491"/>
+    <row r="2492"/>
+    <row r="2493"/>
+    <row r="2494"/>
+    <row r="2495"/>
+    <row r="2496"/>
+    <row r="2497"/>
+    <row r="2498"/>
+    <row r="2499"/>
+    <row r="2500"/>
+    <row r="2501"/>
+    <row r="2502"/>
+    <row r="2503"/>
+    <row r="2504"/>
+    <row r="2505"/>
+    <row r="2506"/>
+    <row r="2507"/>
+    <row r="2508"/>
+    <row r="2509"/>
+    <row r="2510"/>
+    <row r="2511"/>
+    <row r="2512"/>
+    <row r="2513"/>
+    <row r="2514"/>
+    <row r="2515"/>
+    <row r="2516"/>
+    <row r="2517"/>
+    <row r="2518"/>
+    <row r="2519"/>
+    <row r="2520"/>
+    <row r="2521"/>
+    <row r="2522"/>
+    <row r="2523"/>
+    <row r="2524"/>
+    <row r="2525"/>
+    <row r="2526"/>
+    <row r="2527"/>
+    <row r="2528"/>
+    <row r="2529"/>
+    <row r="2530"/>
+    <row r="2531"/>
+    <row r="2532"/>
+    <row r="2533"/>
+    <row r="2534"/>
+    <row r="2535"/>
+    <row r="2536"/>
+    <row r="2537"/>
+    <row r="2538"/>
+    <row r="2539"/>
+    <row r="2540"/>
+    <row r="2541"/>
+    <row r="2542"/>
+    <row r="2543"/>
+    <row r="2544"/>
+    <row r="2545"/>
+    <row r="2546"/>
+    <row r="2547"/>
+    <row r="2548"/>
+    <row r="2549"/>
+    <row r="2550"/>
+    <row r="2551"/>
+    <row r="2552"/>
+    <row r="2553"/>
+    <row r="2554"/>
+    <row r="2555"/>
+    <row r="2556"/>
+    <row r="2557"/>
+    <row r="2558"/>
+    <row r="2559"/>
+    <row r="2560"/>
+    <row r="2561"/>
+    <row r="2562"/>
+    <row r="2563"/>
+    <row r="2564"/>
+    <row r="2565"/>
+    <row r="2566"/>
+    <row r="2567"/>
+    <row r="2568"/>
+    <row r="2569"/>
+    <row r="2570"/>
+    <row r="2571"/>
+    <row r="2572"/>
+    <row r="2573"/>
+    <row r="2574"/>
+    <row r="2575"/>
+    <row r="2576"/>
+    <row r="2577"/>
+    <row r="2578"/>
+    <row r="2579"/>
+    <row r="2580"/>
+    <row r="2581"/>
+    <row r="2582"/>
+    <row r="2583"/>
+    <row r="2584"/>
+    <row r="2585"/>
+    <row r="2586"/>
+    <row r="2587"/>
+    <row r="2588"/>
+    <row r="2589"/>
+    <row r="2590"/>
+    <row r="2591"/>
+    <row r="2592"/>
+    <row r="2593"/>
+    <row r="2594"/>
+    <row r="2595"/>
+    <row r="2596"/>
+    <row r="2597"/>
+    <row r="2598"/>
+    <row r="2599"/>
+    <row r="2600"/>
+    <row r="2601"/>
+    <row r="2602"/>
+    <row r="2603"/>
+    <row r="2604"/>
+    <row r="2605"/>
+    <row r="2606"/>
+    <row r="2607"/>
+    <row r="2608"/>
+    <row r="2609"/>
+    <row r="2610"/>
+    <row r="2611"/>
+    <row r="2612"/>
+    <row r="2613"/>
+    <row r="2614"/>
+    <row r="2615"/>
+    <row r="2616"/>
+    <row r="2617"/>
+    <row r="2618"/>
+    <row r="2619"/>
+    <row r="2620"/>
+    <row r="2621"/>
+    <row r="2622"/>
+    <row r="2623"/>
+    <row r="2624"/>
+    <row r="2625"/>
+    <row r="2626"/>
+    <row r="2627"/>
+    <row r="2628"/>
+    <row r="2629"/>
+    <row r="2630"/>
+    <row r="2631"/>
+    <row r="2632"/>
+    <row r="2633"/>
+    <row r="2634"/>
+    <row r="2635"/>
+    <row r="2636"/>
+    <row r="2637"/>
+    <row r="2638"/>
+    <row r="2639"/>
+    <row r="2640"/>
+    <row r="2641"/>
+    <row r="2642"/>
+    <row r="2643"/>
+    <row r="2644"/>
+    <row r="2645"/>
+    <row r="2646"/>
+    <row r="2647"/>
+    <row r="2648"/>
+    <row r="2649"/>
+    <row r="2650"/>
+    <row r="2651"/>
+    <row r="2652"/>
+    <row r="2653"/>
+    <row r="2654"/>
+    <row r="2655"/>
+    <row r="2656"/>
+    <row r="2657"/>
+    <row r="2658"/>
+    <row r="2659"/>
+    <row r="2660"/>
+    <row r="2661"/>
+    <row r="2662"/>
+    <row r="2663"/>
+    <row r="2664"/>
+    <row r="2665"/>
+    <row r="2666"/>
+    <row r="2667"/>
+    <row r="2668"/>
+    <row r="2669"/>
+    <row r="2670"/>
+    <row r="2671"/>
+    <row r="2672"/>
+    <row r="2673"/>
+    <row r="2674"/>
+    <row r="2675"/>
+    <row r="2676"/>
+    <row r="2677"/>
+    <row r="2678"/>
+    <row r="2679"/>
+    <row r="2680"/>
+    <row r="2681"/>
+    <row r="2682"/>
+    <row r="2683"/>
+    <row r="2684"/>
+    <row r="2685"/>
+    <row r="2686"/>
+    <row r="2687"/>
+    <row r="2688"/>
+    <row r="2689"/>
+    <row r="2690"/>
+    <row r="2691"/>
+    <row r="2692"/>
+    <row r="2693"/>
+    <row r="2694"/>
+    <row r="2695"/>
+    <row r="2696"/>
+    <row r="2697"/>
+    <row r="2698"/>
+    <row r="2699"/>
+    <row r="2700"/>
+    <row r="2701"/>
+    <row r="2702"/>
+    <row r="2703"/>
+    <row r="2704"/>
+    <row r="2705"/>
+    <row r="2706"/>
+    <row r="2707"/>
+    <row r="2708"/>
+    <row r="2709"/>
+    <row r="2710"/>
+    <row r="2711"/>
+    <row r="2712"/>
+    <row r="2713"/>
+    <row r="2714"/>
+    <row r="2715"/>
+    <row r="2716"/>
+    <row r="2717"/>
+    <row r="2718"/>
+    <row r="2719"/>
+    <row r="2720"/>
+    <row r="2721"/>
+    <row r="2722"/>
+    <row r="2723"/>
+    <row r="2724"/>
+    <row r="2725"/>
+    <row r="2726"/>
+    <row r="2727"/>
+    <row r="2728"/>
+    <row r="2729"/>
+    <row r="2730"/>
+    <row r="2731"/>
+    <row r="2732"/>
+    <row r="2733"/>
+    <row r="2734"/>
+    <row r="2735"/>
+    <row r="2736"/>
+    <row r="2737"/>
+    <row r="2738"/>
+    <row r="2739"/>
+    <row r="2740"/>
+    <row r="2741"/>
+    <row r="2742"/>
+    <row r="2743"/>
+    <row r="2744"/>
+    <row r="2745"/>
+    <row r="2746"/>
+    <row r="2747"/>
+    <row r="2748"/>
+    <row r="2749"/>
+    <row r="2750"/>
+    <row r="2751"/>
+    <row r="2752"/>
+    <row r="2753"/>
+    <row r="2754"/>
+    <row r="2755"/>
+    <row r="2756"/>
+    <row r="2757"/>
+    <row r="2758"/>
+    <row r="2759"/>
+    <row r="2760"/>
+    <row r="2761"/>
+    <row r="2762"/>
+    <row r="2763"/>
+    <row r="2764"/>
+    <row r="2765"/>
+    <row r="2766"/>
+    <row r="2767"/>
+    <row r="2768"/>
+    <row r="2769"/>
+    <row r="2770"/>
+    <row r="2771"/>
+    <row r="2772"/>
+    <row r="2773"/>
+    <row r="2774"/>
+    <row r="2775"/>
+    <row r="2776"/>
+    <row r="2777"/>
+    <row r="2778"/>
+    <row r="2779"/>
+    <row r="2780"/>
+    <row r="2781"/>
+    <row r="2782"/>
+    <row r="2783"/>
+    <row r="2784"/>
+    <row r="2785"/>
+    <row r="2786"/>
+    <row r="2787"/>
+    <row r="2788"/>
+    <row r="2789"/>
+    <row r="2790"/>
+    <row r="2791"/>
+    <row r="2792"/>
+    <row r="2793"/>
+    <row r="2794"/>
+    <row r="2795"/>
+    <row r="2796"/>
+    <row r="2797"/>
+    <row r="2798"/>
+    <row r="2799"/>
+    <row r="2800"/>
+    <row r="2801"/>
+    <row r="2802"/>
+    <row r="2803"/>
+    <row r="2804"/>
+    <row r="2805"/>
+    <row r="2806"/>
+    <row r="2807"/>
+    <row r="2808"/>
+    <row r="2809"/>
+    <row r="2810"/>
+    <row r="2811"/>
+    <row r="2812"/>
+    <row r="2813"/>
+    <row r="2814"/>
+    <row r="2815"/>
+    <row r="2816"/>
+    <row r="2817"/>
+    <row r="2818"/>
+    <row r="2819"/>
+    <row r="2820"/>
+    <row r="2821"/>
+    <row r="2822"/>
+    <row r="2823"/>
+    <row r="2824"/>
+    <row r="2825"/>
+    <row r="2826"/>
+    <row r="2827"/>
+    <row r="2828"/>
+    <row r="2829"/>
+    <row r="2830"/>
+    <row r="2831"/>
+    <row r="2832"/>
+    <row r="2833"/>
+    <row r="2834"/>
+    <row r="2835"/>
+    <row r="2836"/>
+    <row r="2837"/>
+    <row r="2838"/>
+    <row r="2839"/>
+    <row r="2840"/>
+    <row r="2841"/>
+    <row r="2842"/>
+    <row r="2843"/>
+    <row r="2844"/>
+    <row r="2845"/>
+    <row r="2846"/>
+    <row r="2847"/>
+    <row r="2848"/>
+    <row r="2849"/>
+    <row r="2850"/>
+    <row r="2851"/>
+    <row r="2852"/>
+    <row r="2853"/>
+    <row r="2854"/>
+    <row r="2855"/>
+    <row r="2856"/>
+    <row r="2857"/>
+    <row r="2858"/>
+    <row r="2859"/>
+    <row r="2860"/>
+    <row r="2861"/>
+    <row r="2862"/>
+    <row r="2863"/>
+    <row r="2864"/>
+    <row r="2865"/>
+    <row r="2866"/>
+    <row r="2867"/>
+    <row r="2868"/>
+    <row r="2869"/>
+    <row r="2870"/>
+    <row r="2871"/>
+    <row r="2872"/>
+    <row r="2873"/>
+    <row r="2874"/>
+    <row r="2875"/>
+    <row r="2876"/>
+    <row r="2877"/>
+    <row r="2878"/>
+    <row r="2879"/>
+    <row r="2880"/>
+    <row r="2881"/>
+    <row r="2882"/>
+    <row r="2883"/>
+    <row r="2884"/>
+    <row r="2885"/>
+    <row r="2886"/>
+    <row r="2887"/>
+    <row r="2888"/>
+    <row r="2889"/>
+    <row r="2890"/>
+    <row r="2891"/>
+    <row r="2892"/>
+    <row r="2893"/>
+    <row r="2894"/>
+    <row r="2895"/>
+    <row r="2896"/>
+    <row r="2897"/>
+    <row r="2898"/>
+    <row r="2899"/>
+    <row r="2900"/>
+    <row r="2901"/>
+    <row r="2902"/>
+    <row r="2903"/>
+    <row r="2904"/>
+    <row r="2905"/>
+    <row r="2906"/>
+    <row r="2907"/>
+    <row r="2908"/>
+    <row r="2909"/>
+    <row r="2910"/>
+    <row r="2911"/>
+    <row r="2912"/>
+    <row r="2913"/>
+    <row r="2914"/>
+    <row r="2915"/>
+    <row r="2916"/>
+    <row r="2917"/>
+    <row r="2918"/>
+    <row r="2919"/>
+    <row r="2920"/>
+    <row r="2921"/>
+    <row r="2922"/>
+    <row r="2923"/>
+    <row r="2924"/>
+    <row r="2925"/>
+    <row r="2926"/>
+    <row r="2927"/>
+    <row r="2928"/>
+    <row r="2929"/>
+    <row r="2930"/>
+    <row r="2931"/>
+    <row r="2932"/>
+    <row r="2933"/>
+    <row r="2934"/>
+    <row r="2935"/>
+    <row r="2936"/>
+    <row r="2937"/>
+    <row r="2938"/>
+    <row r="2939"/>
+    <row r="2940"/>
+    <row r="2941"/>
+    <row r="2942"/>
+    <row r="2943"/>
+    <row r="2944"/>
+    <row r="2945"/>
+    <row r="2946"/>
+    <row r="2947"/>
+    <row r="2948"/>
+    <row r="2949"/>
+    <row r="2950"/>
+    <row r="2951"/>
+    <row r="2952"/>
+    <row r="2953"/>
+    <row r="2954"/>
+    <row r="2955"/>
+    <row r="2956"/>
+    <row r="2957"/>
+    <row r="2958"/>
+    <row r="2959"/>
+    <row r="2960"/>
+    <row r="2961"/>
+    <row r="2962"/>
+    <row r="2963"/>
+    <row r="2964"/>
+    <row r="2965"/>
+    <row r="2966"/>
+    <row r="2967"/>
+    <row r="2968"/>
+    <row r="2969"/>
+    <row r="2970"/>
+    <row r="2971"/>
+    <row r="2972"/>
+    <row r="2973"/>
+    <row r="2974"/>
+    <row r="2975"/>
+    <row r="2976"/>
+    <row r="2977"/>
+    <row r="2978"/>
+    <row r="2979"/>
+    <row r="2980"/>
+    <row r="2981"/>
+    <row r="2982"/>
+    <row r="2983"/>
+    <row r="2984"/>
+    <row r="2985"/>
+    <row r="2986"/>
+    <row r="2987"/>
+    <row r="2988"/>
+    <row r="2989"/>
+    <row r="2990"/>
+    <row r="2991"/>
+    <row r="2992"/>
+    <row r="2993"/>
+    <row r="2994"/>
+    <row r="2995"/>
+    <row r="2996"/>
+    <row r="2997"/>
+    <row r="2998"/>
+    <row r="2999"/>
+    <row r="3000"/>
+    <row r="3001"/>
+    <row r="3002"/>
+    <row r="3003"/>
+    <row r="3004"/>
+    <row r="3005"/>
+    <row r="3006"/>
+    <row r="3007"/>
+    <row r="3008"/>
+    <row r="3009"/>
+    <row r="3010"/>
+    <row r="3011"/>
+    <row r="3012"/>
+    <row r="3013"/>
+    <row r="3014"/>
+    <row r="3015"/>
+    <row r="3016"/>
+    <row r="3017"/>
+    <row r="3018"/>
+    <row r="3019"/>
+    <row r="3020"/>
+    <row r="3021"/>
+    <row r="3022"/>
+    <row r="3023"/>
+    <row r="3024"/>
+    <row r="3025"/>
+    <row r="3026"/>
+    <row r="3027"/>
+    <row r="3028"/>
+    <row r="3029"/>
+    <row r="3030"/>
+    <row r="3031"/>
+    <row r="3032"/>
+    <row r="3033"/>
+    <row r="3034"/>
+    <row r="3035"/>
+    <row r="3036"/>
+    <row r="3037"/>
+    <row r="3038"/>
+    <row r="3039"/>
+    <row r="3040"/>
+    <row r="3041"/>
+    <row r="3042"/>
+    <row r="3043"/>
+    <row r="3044"/>
+    <row r="3045"/>
+    <row r="3046"/>
+    <row r="3047"/>
+    <row r="3048"/>
+    <row r="3049"/>
+    <row r="3050"/>
+    <row r="3051"/>
+    <row r="3052"/>
+    <row r="3053"/>
+    <row r="3054"/>
+    <row r="3055"/>
+    <row r="3056"/>
+    <row r="3057"/>
+    <row r="3058"/>
+    <row r="3059"/>
+    <row r="3060"/>
+    <row r="3061"/>
+    <row r="3062"/>
+    <row r="3063"/>
+    <row r="3064"/>
+    <row r="3065"/>
+    <row r="3066"/>
+    <row r="3067"/>
+    <row r="3068"/>
+    <row r="3069"/>
+    <row r="3070"/>
+    <row r="3071"/>
+    <row r="3072"/>
+    <row r="3073"/>
+    <row r="3074"/>
+    <row r="3075"/>
+    <row r="3076"/>
+    <row r="3077"/>
+    <row r="3078"/>
+    <row r="3079"/>
+    <row r="3080"/>
+    <row r="3081"/>
+    <row r="3082"/>
+    <row r="3083"/>
+    <row r="3084"/>
+    <row r="3085"/>
+    <row r="3086"/>
+    <row r="3087"/>
+    <row r="3088"/>
+    <row r="3089"/>
+    <row r="3090"/>
+    <row r="3091"/>
+    <row r="3092"/>
+    <row r="3093"/>
+    <row r="3094"/>
+    <row r="3095"/>
+    <row r="3096"/>
+    <row r="3097"/>
+    <row r="3098"/>
+    <row r="3099"/>
+    <row r="3100"/>
+    <row r="3101"/>
+    <row r="3102"/>
+    <row r="3103"/>
+    <row r="3104"/>
+    <row r="3105"/>
+    <row r="3106"/>
+    <row r="3107"/>
+    <row r="3108"/>
+    <row r="3109"/>
+    <row r="3110"/>
+    <row r="3111"/>
+    <row r="3112"/>
+    <row r="3113"/>
+    <row r="3114"/>
+    <row r="3115"/>
+    <row r="3116"/>
+    <row r="3117"/>
+    <row r="3118"/>
+    <row r="3119"/>
+    <row r="3120"/>
+    <row r="3121"/>
+    <row r="3122"/>
+    <row r="3123"/>
+    <row r="3124"/>
+    <row r="3125"/>
+    <row r="3126"/>
+    <row r="3127"/>
+    <row r="3128"/>
+    <row r="3129"/>
+    <row r="3130"/>
+    <row r="3131"/>
+    <row r="3132"/>
+    <row r="3133"/>
+    <row r="3134"/>
+    <row r="3135"/>
+    <row r="3136"/>
+    <row r="3137"/>
+    <row r="3138"/>
+    <row r="3139"/>
+    <row r="3140"/>
+    <row r="3141"/>
+    <row r="3142"/>
+    <row r="3143"/>
+    <row r="3144"/>
+    <row r="3145"/>
+    <row r="3146"/>
+    <row r="3147"/>
+    <row r="3148"/>
+    <row r="3149"/>
+    <row r="3150"/>
+    <row r="3151"/>
+    <row r="3152"/>
+    <row r="3153"/>
+    <row r="3154"/>
+    <row r="3155"/>
+    <row r="3156"/>
+    <row r="3157"/>
+    <row r="3158"/>
+    <row r="3159"/>
+    <row r="3160"/>
+    <row r="3161"/>
+    <row r="3162"/>
+    <row r="3163"/>
+    <row r="3164"/>
+    <row r="3165"/>
+    <row r="3166"/>
+    <row r="3167"/>
+    <row r="3168"/>
+    <row r="3169"/>
+    <row r="3170"/>
+    <row r="3171"/>
+    <row r="3172"/>
+    <row r="3173"/>
+    <row r="3174"/>
+    <row r="3175"/>
+    <row r="3176"/>
+    <row r="3177"/>
+    <row r="3178"/>
+    <row r="3179"/>
+    <row r="3180"/>
+    <row r="3181"/>
+    <row r="3182"/>
+    <row r="3183"/>
+    <row r="3184"/>
+    <row r="3185"/>
+    <row r="3186"/>
+    <row r="3187"/>
+    <row r="3188"/>
+    <row r="3189"/>
+    <row r="3190"/>
+    <row r="3191"/>
+    <row r="3192"/>
+    <row r="3193"/>
+    <row r="3194"/>
+    <row r="3195"/>
+    <row r="3196"/>
+    <row r="3197"/>
+    <row r="3198"/>
+    <row r="3199"/>
+    <row r="3200"/>
+    <row r="3201"/>
+    <row r="3202"/>
+    <row r="3203"/>
+    <row r="3204"/>
+    <row r="3205"/>
+    <row r="3206"/>
+    <row r="3207"/>
+    <row r="3208"/>
+    <row r="3209"/>
+    <row r="3210"/>
+    <row r="3211"/>
+    <row r="3212"/>
+    <row r="3213"/>
+    <row r="3214"/>
+    <row r="3215"/>
+    <row r="3216"/>
+    <row r="3217"/>
+    <row r="3218"/>
+    <row r="3219"/>
+    <row r="3220"/>
+    <row r="3221"/>
+    <row r="3222"/>
+    <row r="3223"/>
+    <row r="3224"/>
+    <row r="3225"/>
+    <row r="3226"/>
+    <row r="3227"/>
+    <row r="3228"/>
+    <row r="3229"/>
+    <row r="3230"/>
+    <row r="3231"/>
+    <row r="3232"/>
+    <row r="3233"/>
+    <row r="3234"/>
+    <row r="3235"/>
+    <row r="3236"/>
+    <row r="3237"/>
+    <row r="3238"/>
+    <row r="3239"/>
+    <row r="3240"/>
+    <row r="3241"/>
+    <row r="3242"/>
+    <row r="3243"/>
+    <row r="3244"/>
+    <row r="3245"/>
+    <row r="3246"/>
+    <row r="3247"/>
+    <row r="3248"/>
+    <row r="3249"/>
+    <row r="3250"/>
+    <row r="3251"/>
+    <row r="3252"/>
+    <row r="3253"/>
+    <row r="3254"/>
+    <row r="3255"/>
+    <row r="3256"/>
+    <row r="3257"/>
+    <row r="3258"/>
+    <row r="3259"/>
+    <row r="3260"/>
+    <row r="3261"/>
+    <row r="3262"/>
+    <row r="3263"/>
+    <row r="3264"/>
+    <row r="3265"/>
+    <row r="3266"/>
+    <row r="3267"/>
+    <row r="3268"/>
+    <row r="3269"/>
+    <row r="3270"/>
+    <row r="3271"/>
+    <row r="3272"/>
+    <row r="3273"/>
+    <row r="3274"/>
+    <row r="3275"/>
+    <row r="3276"/>
+    <row r="3277"/>
+    <row r="3278"/>
+    <row r="3279"/>
+    <row r="3280"/>
+    <row r="3281"/>
+    <row r="3282"/>
+    <row r="3283"/>
+    <row r="3284"/>
+    <row r="3285"/>
+    <row r="3286"/>
+    <row r="3287"/>
+    <row r="3288"/>
+    <row r="3289"/>
+    <row r="3290"/>
+    <row r="3291"/>
+    <row r="3292"/>
+    <row r="3293"/>
+    <row r="3294"/>
+    <row r="3295"/>
+    <row r="3296"/>
+    <row r="3297"/>
+    <row r="3298"/>
+    <row r="3299"/>
+    <row r="3300"/>
+    <row r="3301"/>
+    <row r="3302"/>
+    <row r="3303"/>
+    <row r="3304"/>
+    <row r="3305"/>
+    <row r="3306"/>
+    <row r="3307"/>
+    <row r="3308"/>
+    <row r="3309"/>
+    <row r="3310"/>
+    <row r="3311"/>
+    <row r="3312"/>
+    <row r="3313"/>
+    <row r="3314"/>
+    <row r="3315"/>
+    <row r="3316"/>
+    <row r="3317"/>
+    <row r="3318"/>
+    <row r="3319"/>
+    <row r="3320"/>
+    <row r="3321"/>
+    <row r="3322"/>
+    <row r="3323"/>
+    <row r="3324"/>
+    <row r="3325"/>
+    <row r="3326"/>
+    <row r="3327"/>
+    <row r="3328"/>
+    <row r="3329"/>
+    <row r="3330"/>
+    <row r="3331"/>
+    <row r="3332"/>
+    <row r="3333"/>
+    <row r="3334"/>
+    <row r="3335"/>
+    <row r="3336"/>
+    <row r="3337"/>
+    <row r="3338"/>
+    <row r="3339"/>
+    <row r="3340"/>
+    <row r="3341"/>
+    <row r="3342"/>
+    <row r="3343"/>
+    <row r="3344"/>
+    <row r="3345"/>
+    <row r="3346"/>
+    <row r="3347"/>
+    <row r="3348"/>
+    <row r="3349"/>
+    <row r="3350"/>
+    <row r="3351"/>
+    <row r="3352"/>
+    <row r="3353"/>
+    <row r="3354"/>
+    <row r="3355"/>
+    <row r="3356"/>
+    <row r="3357"/>
+    <row r="3358"/>
+    <row r="3359"/>
+    <row r="3360"/>
+    <row r="3361"/>
+    <row r="3362"/>
+    <row r="3363"/>
+    <row r="3364"/>
+    <row r="3365"/>
+    <row r="3366"/>
+    <row r="3367"/>
+    <row r="3368"/>
+    <row r="3369"/>
+    <row r="3370"/>
+    <row r="3371"/>
+    <row r="3372"/>
+    <row r="3373"/>
+    <row r="3374"/>
+    <row r="3375"/>
+    <row r="3376"/>
+    <row r="3377"/>
+    <row r="3378"/>
+    <row r="3379"/>
+    <row r="3380"/>
+    <row r="3381"/>
+    <row r="3382"/>
+    <row r="3383"/>
+    <row r="3384"/>
+    <row r="3385"/>
+    <row r="3386"/>
+    <row r="3387"/>
+    <row r="3388"/>
+    <row r="3389"/>
+    <row r="3390"/>
+    <row r="3391"/>
+    <row r="3392"/>
+    <row r="3393"/>
+    <row r="3394"/>
+    <row r="3395"/>
+    <row r="3396"/>
+    <row r="3397"/>
+    <row r="3398"/>
+    <row r="3399"/>
+    <row r="3400"/>
+    <row r="3401"/>
+    <row r="3402"/>
+    <row r="3403"/>
+    <row r="3404"/>
+    <row r="3405"/>
+    <row r="3406"/>
+    <row r="3407"/>
+    <row r="3408"/>
+    <row r="3409"/>
+    <row r="3410"/>
+    <row r="3411"/>
+    <row r="3412"/>
+    <row r="3413"/>
+    <row r="3414"/>
+    <row r="3415"/>
+    <row r="3416"/>
+    <row r="3417"/>
+    <row r="3418"/>
+    <row r="3419"/>
+    <row r="3420"/>
+    <row r="3421"/>
+    <row r="3422"/>
+    <row r="3423"/>
+    <row r="3424"/>
+    <row r="3425"/>
+    <row r="3426"/>
+    <row r="3427"/>
+    <row r="3428"/>
+    <row r="3429"/>
+    <row r="3430"/>
+    <row r="3431"/>
+    <row r="3432"/>
+    <row r="3433"/>
+    <row r="3434"/>
+    <row r="3435"/>
+    <row r="3436"/>
+    <row r="3437"/>
+    <row r="3438"/>
+    <row r="3439"/>
+    <row r="3440"/>
+    <row r="3441"/>
+    <row r="3442"/>
+    <row r="3443"/>
+    <row r="3444"/>
+    <row r="3445"/>
+    <row r="3446"/>
+    <row r="3447"/>
+    <row r="3448"/>
+    <row r="3449"/>
+    <row r="3450"/>
+    <row r="3451"/>
+    <row r="3452"/>
+    <row r="3453"/>
+    <row r="3454"/>
+    <row r="3455"/>
+    <row r="3456"/>
+    <row r="3457"/>
+    <row r="3458"/>
+    <row r="3459"/>
+    <row r="3460"/>
+    <row r="3461"/>
+    <row r="3462"/>
+    <row r="3463"/>
+    <row r="3464"/>
+    <row r="3465"/>
+    <row r="3466"/>
+    <row r="3467"/>
+    <row r="3468"/>
+    <row r="3469"/>
+    <row r="3470"/>
+    <row r="3471"/>
+    <row r="3472"/>
+    <row r="3473"/>
+    <row r="3474"/>
+    <row r="3475"/>
+    <row r="3476"/>
+    <row r="3477"/>
+    <row r="3478"/>
+    <row r="3479"/>
+    <row r="3480"/>
+    <row r="3481"/>
+    <row r="3482"/>
+    <row r="3483"/>
+    <row r="3484"/>
+    <row r="3485"/>
+    <row r="3486"/>
+    <row r="3487"/>
+    <row r="3488"/>
+    <row r="3489"/>
+    <row r="3490"/>
+    <row r="3491"/>
+    <row r="3492"/>
+    <row r="3493"/>
+    <row r="3494"/>
+    <row r="3495"/>
+    <row r="3496"/>
+    <row r="3497"/>
+    <row r="3498"/>
+    <row r="3499"/>
+    <row r="3500"/>
+    <row r="3501"/>
+    <row r="3502"/>
+    <row r="3503"/>
+    <row r="3504"/>
+    <row r="3505"/>
+    <row r="3506"/>
+    <row r="3507"/>
+    <row r="3508"/>
+    <row r="3509"/>
+    <row r="3510"/>
+    <row r="3511"/>
+    <row r="3512"/>
+    <row r="3513"/>
+    <row r="3514"/>
+    <row r="3515"/>
+    <row r="3516"/>
+    <row r="3517"/>
+    <row r="3518"/>
+    <row r="3519"/>
+    <row r="3520"/>
+    <row r="3521"/>
+    <row r="3522"/>
+    <row r="3523"/>
+    <row r="3524"/>
+    <row r="3525"/>
+    <row r="3526"/>
+    <row r="3527"/>
+    <row r="3528"/>
+    <row r="3529"/>
+    <row r="3530"/>
+    <row r="3531"/>
+    <row r="3532"/>
+    <row r="3533"/>
+    <row r="3534"/>
+    <row r="3535"/>
+    <row r="3536"/>
+    <row r="3537"/>
+    <row r="3538"/>
+    <row r="3539"/>
+    <row r="3540"/>
+    <row r="3541"/>
+    <row r="3542"/>
+    <row r="3543"/>
+    <row r="3544"/>
+    <row r="3545"/>
+    <row r="3546"/>
+    <row r="3547"/>
+    <row r="3548"/>
+    <row r="3549"/>
+    <row r="3550"/>
+    <row r="3551"/>
+    <row r="3552"/>
+    <row r="3553"/>
+    <row r="3554"/>
+    <row r="3555"/>
+    <row r="3556"/>
+    <row r="3557"/>
+    <row r="3558"/>
+    <row r="3559"/>
+    <row r="3560"/>
+    <row r="3561"/>
+    <row r="3562"/>
+    <row r="3563"/>
+    <row r="3564"/>
+    <row r="3565"/>
+    <row r="3566"/>
+    <row r="3567"/>
+    <row r="3568"/>
+    <row r="3569"/>
+    <row r="3570"/>
+    <row r="3571"/>
+    <row r="3572"/>
+    <row r="3573"/>
+    <row r="3574"/>
+    <row r="3575"/>
+    <row r="3576"/>
+    <row r="3577"/>
+    <row r="3578"/>
+    <row r="3579"/>
+    <row r="3580"/>
+    <row r="3581"/>
+    <row r="3582"/>
+    <row r="3583"/>
+    <row r="3584"/>
+    <row r="3585"/>
+    <row r="3586"/>
+    <row r="3587"/>
+    <row r="3588"/>
+    <row r="3589"/>
+    <row r="3590"/>
+    <row r="3591"/>
+    <row r="3592"/>
+    <row r="3593"/>
+    <row r="3594"/>
+    <row r="3595"/>
+    <row r="3596"/>
+    <row r="3597"/>
+    <row r="3598"/>
+    <row r="3599"/>
+    <row r="3600"/>
+    <row r="3601"/>
+    <row r="3602"/>
+    <row r="3603"/>
+    <row r="3604"/>
+    <row r="3605"/>
+    <row r="3606"/>
+    <row r="3607"/>
+    <row r="3608"/>
+    <row r="3609"/>
+    <row r="3610"/>
+    <row r="3611"/>
+    <row r="3612"/>
+    <row r="3613"/>
+    <row r="3614"/>
+    <row r="3615"/>
+    <row r="3616"/>
+    <row r="3617"/>
+    <row r="3618"/>
+    <row r="3619"/>
+    <row r="3620"/>
+    <row r="3621"/>
+    <row r="3622"/>
+    <row r="3623"/>
+    <row r="3624"/>
+    <row r="3625"/>
+    <row r="3626"/>
+    <row r="3627"/>
+    <row r="3628"/>
+    <row r="3629"/>
+    <row r="3630"/>
+    <row r="3631"/>
+    <row r="3632"/>
+    <row r="3633"/>
+    <row r="3634"/>
+    <row r="3635"/>
+    <row r="3636"/>
+    <row r="3637"/>
+    <row r="3638"/>
+    <row r="3639"/>
+    <row r="3640"/>
+    <row r="3641"/>
+    <row r="3642"/>
+    <row r="3643"/>
+    <row r="3644"/>
+    <row r="3645"/>
+    <row r="3646"/>
+    <row r="3647"/>
+    <row r="3648"/>
+    <row r="3649"/>
+    <row r="3650"/>
+    <row r="3651"/>
+    <row r="3652"/>
+    <row r="3653"/>
+    <row r="3654"/>
+    <row r="3655"/>
+    <row r="3656"/>
+    <row r="3657"/>
+    <row r="3658"/>
+    <row r="3659"/>
+    <row r="3660"/>
+    <row r="3661"/>
+    <row r="3662"/>
+    <row r="3663"/>
+    <row r="3664"/>
+    <row r="3665"/>
+    <row r="3666"/>
+    <row r="3667"/>
+    <row r="3668"/>
+    <row r="3669"/>
+    <row r="3670"/>
+    <row r="3671"/>
+    <row r="3672"/>
+    <row r="3673"/>
+    <row r="3674"/>
+    <row r="3675"/>
+    <row r="3676"/>
+    <row r="3677"/>
+    <row r="3678"/>
+    <row r="3679"/>
+    <row r="3680"/>
+    <row r="3681"/>
+    <row r="3682"/>
+    <row r="3683"/>
+    <row r="3684"/>
+    <row r="3685"/>
+    <row r="3686"/>
+    <row r="3687"/>
+    <row r="3688"/>
+    <row r="3689"/>
+    <row r="3690"/>
+    <row r="3691"/>
+    <row r="3692"/>
+    <row r="3693"/>
+    <row r="3694"/>
+    <row r="3695"/>
+    <row r="3696"/>
+    <row r="3697"/>
+    <row r="3698"/>
+    <row r="3699"/>
+    <row r="3700"/>
+    <row r="3701"/>
+    <row r="3702"/>
+    <row r="3703"/>
+    <row r="3704"/>
+    <row r="3705"/>
+    <row r="3706"/>
+    <row r="3707"/>
+    <row r="3708"/>
+    <row r="3709"/>
+    <row r="3710"/>
+    <row r="3711"/>
+    <row r="3712"/>
+    <row r="3713"/>
+    <row r="3714"/>
+    <row r="3715"/>
+    <row r="3716"/>
+    <row r="3717"/>
+    <row r="3718"/>
+    <row r="3719"/>
+    <row r="3720"/>
+    <row r="3721"/>
+    <row r="3722"/>
+    <row r="3723"/>
+    <row r="3724"/>
+    <row r="3725"/>
+    <row r="3726"/>
+    <row r="3727"/>
+    <row r="3728"/>
+    <row r="3729"/>
+    <row r="3730"/>
+    <row r="3731"/>
+    <row r="3732"/>
+    <row r="3733"/>
+    <row r="3734"/>
+    <row r="3735"/>
+    <row r="3736"/>
+    <row r="3737"/>
+    <row r="3738"/>
+    <row r="3739"/>
+    <row r="3740"/>
+    <row r="3741"/>
+    <row r="3742"/>
+    <row r="3743"/>
+    <row r="3744"/>
+    <row r="3745"/>
+    <row r="3746"/>
+    <row r="3747"/>
+    <row r="3748"/>
+    <row r="3749"/>
+    <row r="3750"/>
+    <row r="3751"/>
+    <row r="3752"/>
+    <row r="3753"/>
+    <row r="3754"/>
+    <row r="3755"/>
+    <row r="3756"/>
+    <row r="3757"/>
+    <row r="3758"/>
+    <row r="3759"/>
+    <row r="3760"/>
+    <row r="3761"/>
+    <row r="3762"/>
+    <row r="3763"/>
+    <row r="3764"/>
+    <row r="3765"/>
+    <row r="3766"/>
+    <row r="3767"/>
+    <row r="3768"/>
+    <row r="3769"/>
+    <row r="3770"/>
+    <row r="3771"/>
+    <row r="3772"/>
+    <row r="3773"/>
+    <row r="3774"/>
+    <row r="3775"/>
+    <row r="3776"/>
+    <row r="3777"/>
+    <row r="3778"/>
+    <row r="3779"/>
+    <row r="3780"/>
+    <row r="3781"/>
+    <row r="3782"/>
+    <row r="3783"/>
+    <row r="3784"/>
+    <row r="3785"/>
+    <row r="3786"/>
+    <row r="3787"/>
+    <row r="3788"/>
+    <row r="3789"/>
+    <row r="3790"/>
+    <row r="3791"/>
+    <row r="3792"/>
+    <row r="3793"/>
+    <row r="3794"/>
+    <row r="3795"/>
+    <row r="3796"/>
+    <row r="3797"/>
+    <row r="3798"/>
+    <row r="3799"/>
+    <row r="3800"/>
+    <row r="3801"/>
+    <row r="3802"/>
+    <row r="3803"/>
+    <row r="3804"/>
+    <row r="3805"/>
+    <row r="3806"/>
+    <row r="3807"/>
+    <row r="3808"/>
+    <row r="3809"/>
+    <row r="3810"/>
+    <row r="3811"/>
+    <row r="3812"/>
+    <row r="3813"/>
+    <row r="3814"/>
+    <row r="3815"/>
+    <row r="3816"/>
+    <row r="3817"/>
+    <row r="3818"/>
+    <row r="3819"/>
+    <row r="3820"/>
+    <row r="3821"/>
+    <row r="3822"/>
+    <row r="3823"/>
+    <row r="3824"/>
+    <row r="3825"/>
+    <row r="3826"/>
+    <row r="3827"/>
+    <row r="3828"/>
+    <row r="3829"/>
+    <row r="3830"/>
+    <row r="3831"/>
+    <row r="3832"/>
+    <row r="3833"/>
+    <row r="3834"/>
+    <row r="3835"/>
+    <row r="3836"/>
+    <row r="3837"/>
+    <row r="3838"/>
+    <row r="3839"/>
+    <row r="3840"/>
+    <row r="3841"/>
+    <row r="3842"/>
+    <row r="3843"/>
+    <row r="3844"/>
+    <row r="3845"/>
+    <row r="3846"/>
+    <row r="3847"/>
+    <row r="3848"/>
+    <row r="3849"/>
+    <row r="3850"/>
+    <row r="3851"/>
+    <row r="3852"/>
+    <row r="3853"/>
+    <row r="3854"/>
+    <row r="3855"/>
+    <row r="3856"/>
+    <row r="3857"/>
+    <row r="3858"/>
+    <row r="3859"/>
+    <row r="3860"/>
+    <row r="3861"/>
+    <row r="3862"/>
+    <row r="3863"/>
+    <row r="3864"/>
+    <row r="3865"/>
+    <row r="3866"/>
+    <row r="3867"/>
+    <row r="3868"/>
+    <row r="3869"/>
+    <row r="3870"/>
+    <row r="3871"/>
+    <row r="3872"/>
+    <row r="3873"/>
+    <row r="3874"/>
+    <row r="3875"/>
+    <row r="3876"/>
+    <row r="3877"/>
+    <row r="3878"/>
+    <row r="3879"/>
+    <row r="3880"/>
+    <row r="3881"/>
+    <row r="3882"/>
+    <row r="3883"/>
+    <row r="3884"/>
+    <row r="3885"/>
+    <row r="3886"/>
+    <row r="3887"/>
+    <row r="3888"/>
+    <row r="3889"/>
+    <row r="3890"/>
+    <row r="3891"/>
+    <row r="3892"/>
+    <row r="3893"/>
+    <row r="3894"/>
+    <row r="3895"/>
+    <row r="3896"/>
+    <row r="3897"/>
+    <row r="3898"/>
+    <row r="3899"/>
+    <row r="3900"/>
+    <row r="3901"/>
+    <row r="3902"/>
+    <row r="3903"/>
+    <row r="3904"/>
+    <row r="3905"/>
+    <row r="3906"/>
+    <row r="3907"/>
+    <row r="3908"/>
+    <row r="3909"/>
+    <row r="3910"/>
+    <row r="3911"/>
+    <row r="3912"/>
+    <row r="3913"/>
+    <row r="3914"/>
+    <row r="3915"/>
+    <row r="3916"/>
+    <row r="3917"/>
+    <row r="3918"/>
+    <row r="3919"/>
+    <row r="3920"/>
+    <row r="3921"/>
+    <row r="3922"/>
+    <row r="3923"/>
+    <row r="3924"/>
+    <row r="3925"/>
+    <row r="3926"/>
+    <row r="3927"/>
+    <row r="3928"/>
+    <row r="3929"/>
+    <row r="3930"/>
+    <row r="3931"/>
+    <row r="3932"/>
+    <row r="3933"/>
+    <row r="3934"/>
+    <row r="3935"/>
+    <row r="3936"/>
+    <row r="3937"/>
+    <row r="3938"/>
+    <row r="3939"/>
+    <row r="3940"/>
+    <row r="3941"/>
+    <row r="3942"/>
+    <row r="3943"/>
+    <row r="3944"/>
+    <row r="3945"/>
+    <row r="3946"/>
+    <row r="3947"/>
+    <row r="3948"/>
+    <row r="3949"/>
+    <row r="3950"/>
+    <row r="3951"/>
+    <row r="3952"/>
+    <row r="3953"/>
+    <row r="3954"/>
+    <row r="3955"/>
+    <row r="3956"/>
+    <row r="3957"/>
+    <row r="3958"/>
+    <row r="3959"/>
+    <row r="3960"/>
+    <row r="3961"/>
+    <row r="3962"/>
+    <row r="3963"/>
+    <row r="3964"/>
+    <row r="3965"/>
+    <row r="3966"/>
+    <row r="3967"/>
+    <row r="3968"/>
+    <row r="3969"/>
+    <row r="3970"/>
+    <row r="3971"/>
+    <row r="3972"/>
+    <row r="3973"/>
+    <row r="3974"/>
+    <row r="3975"/>
+    <row r="3976"/>
+    <row r="3977"/>
+    <row r="3978"/>
+    <row r="3979"/>
+    <row r="3980"/>
+    <row r="3981"/>
+    <row r="3982"/>
+    <row r="3983"/>
+    <row r="3984"/>
+    <row r="3985"/>
+    <row r="3986"/>
+    <row r="3987"/>
+    <row r="3988"/>
+    <row r="3989"/>
+    <row r="3990"/>
+    <row r="3991"/>
+    <row r="3992"/>
+    <row r="3993"/>
+    <row r="3994"/>
+    <row r="3995"/>
+    <row r="3996"/>
+    <row r="3997"/>
+    <row r="3998"/>
+    <row r="3999"/>
+    <row r="4000"/>
+    <row r="4001"/>
+    <row r="4002"/>
+    <row r="4003"/>
+    <row r="4004"/>
+    <row r="4005"/>
+    <row r="4006"/>
+    <row r="4007"/>
+    <row r="4008"/>
+    <row r="4009"/>
+    <row r="4010"/>
+    <row r="4011"/>
+    <row r="4012"/>
+    <row r="4013"/>
+    <row r="4014"/>
+    <row r="4015"/>
+    <row r="4016"/>
+    <row r="4017"/>
+    <row r="4018"/>
+    <row r="4019"/>
+    <row r="4020"/>
+    <row r="4021"/>
+    <row r="4022"/>
+    <row r="4023"/>
+    <row r="4024"/>
+    <row r="4025"/>
+    <row r="4026"/>
+    <row r="4027"/>
+    <row r="4028"/>
+    <row r="4029"/>
+    <row r="4030"/>
+    <row r="4031"/>
+    <row r="4032"/>
+    <row r="4033"/>
+    <row r="4034"/>
+    <row r="4035"/>
+    <row r="4036"/>
+    <row r="4037"/>
+    <row r="4038"/>
+    <row r="4039"/>
+    <row r="4040"/>
+    <row r="4041"/>
+    <row r="4042"/>
+    <row r="4043"/>
+    <row r="4044"/>
+    <row r="4045"/>
+    <row r="4046"/>
+    <row r="4047"/>
+    <row r="4048"/>
+    <row r="4049"/>
+    <row r="4050"/>
+    <row r="4051"/>
+    <row r="4052"/>
+    <row r="4053"/>
+    <row r="4054"/>
+    <row r="4055"/>
+    <row r="4056"/>
+    <row r="4057"/>
+    <row r="4058"/>
+    <row r="4059"/>
+    <row r="4060"/>
+    <row r="4061"/>
+    <row r="4062"/>
+    <row r="4063"/>
+    <row r="4064"/>
+    <row r="4065"/>
+    <row r="4066"/>
+    <row r="4067"/>
+    <row r="4068"/>
+    <row r="4069"/>
+    <row r="4070"/>
+    <row r="4071"/>
+    <row r="4072"/>
+    <row r="4073"/>
+    <row r="4074"/>
+    <row r="4075"/>
+    <row r="4076"/>
+    <row r="4077"/>
+    <row r="4078"/>
+    <row r="4079"/>
+    <row r="4080"/>
+    <row r="4081"/>
+    <row r="4082"/>
+    <row r="4083"/>
+    <row r="4084"/>
+    <row r="4085"/>
+    <row r="4086"/>
+    <row r="4087"/>
+    <row r="4088"/>
+    <row r="4089"/>
+    <row r="4090"/>
+    <row r="4091"/>
+    <row r="4092"/>
+    <row r="4093"/>
+    <row r="4094"/>
+    <row r="4095"/>
+    <row r="4096"/>
+    <row r="4097"/>
+    <row r="4098"/>
+    <row r="4099"/>
+    <row r="4100"/>
+    <row r="4101"/>
+    <row r="4102"/>
+    <row r="4103"/>
+    <row r="4104"/>
+    <row r="4105"/>
+    <row r="4106"/>
+    <row r="4107"/>
+    <row r="4108"/>
+    <row r="4109"/>
+    <row r="4110"/>
+    <row r="4111"/>
+    <row r="4112"/>
+    <row r="4113"/>
+    <row r="4114"/>
+    <row r="4115"/>
+    <row r="4116"/>
+    <row r="4117"/>
+    <row r="4118"/>
+    <row r="4119"/>
+    <row r="4120"/>
+    <row r="4121"/>
+    <row r="4122"/>
+    <row r="4123"/>
+    <row r="4124"/>
+    <row r="4125"/>
+    <row r="4126"/>
+    <row r="4127"/>
+    <row r="4128"/>
+    <row r="4129"/>
+    <row r="4130"/>
+    <row r="4131"/>
+    <row r="4132"/>
+    <row r="4133"/>
+    <row r="4134"/>
+    <row r="4135"/>
+    <row r="4136"/>
+    <row r="4137"/>
+    <row r="4138"/>
+    <row r="4139"/>
+    <row r="4140"/>
+    <row r="4141"/>
+    <row r="4142"/>
+    <row r="4143"/>
+    <row r="4144"/>
+    <row r="4145"/>
+    <row r="4146"/>
+    <row r="4147"/>
+    <row r="4148"/>
+    <row r="4149"/>
+    <row r="4150"/>
+    <row r="4151"/>
+    <row r="4152"/>
+    <row r="4153"/>
+    <row r="4154"/>
+    <row r="4155"/>
+    <row r="4156"/>
+    <row r="4157"/>
+    <row r="4158"/>
+    <row r="4159"/>
+    <row r="4160"/>
+    <row r="4161"/>
+    <row r="4162"/>
+    <row r="4163"/>
+    <row r="4164"/>
+    <row r="4165"/>
+    <row r="4166"/>
+    <row r="4167"/>
+    <row r="4168"/>
+    <row r="4169"/>
+    <row r="4170"/>
+    <row r="4171"/>
+    <row r="4172"/>
+    <row r="4173"/>
+    <row r="4174"/>
+    <row r="4175"/>
+    <row r="4176"/>
+    <row r="4177"/>
+    <row r="4178"/>
+    <row r="4179"/>
+    <row r="4180"/>
+    <row r="4181"/>
+    <row r="4182"/>
+    <row r="4183"/>
+    <row r="4184"/>
+    <row r="4185"/>
+    <row r="4186"/>
+    <row r="4187"/>
+    <row r="4188"/>
+    <row r="4189"/>
+    <row r="4190"/>
+    <row r="4191"/>
+    <row r="4192"/>
+    <row r="4193"/>
+    <row r="4194"/>
+    <row r="4195"/>
+    <row r="4196"/>
+    <row r="4197"/>
+    <row r="4198"/>
+    <row r="4199"/>
+    <row r="4200"/>
+    <row r="4201"/>
+    <row r="4202"/>
+    <row r="4203"/>
+    <row r="4204"/>
+    <row r="4205"/>
+    <row r="4206"/>
+    <row r="4207"/>
+    <row r="4208"/>
+    <row r="4209"/>
+    <row r="4210"/>
+    <row r="4211"/>
+    <row r="4212"/>
+    <row r="4213"/>
+    <row r="4214"/>
+    <row r="4215"/>
+    <row r="4216"/>
+    <row r="4217"/>
+    <row r="4218"/>
+    <row r="4219"/>
+    <row r="4220"/>
+    <row r="4221"/>
+    <row r="4222"/>
+    <row r="4223"/>
+    <row r="4224"/>
+    <row r="4225"/>
+    <row r="4226"/>
+    <row r="4227"/>
+    <row r="4228"/>
+    <row r="4229"/>
+    <row r="4230"/>
+    <row r="4231"/>
+    <row r="4232"/>
+    <row r="4233"/>
+    <row r="4234"/>
+    <row r="4235"/>
+    <row r="4236"/>
+    <row r="4237"/>
+    <row r="4238"/>
+    <row r="4239"/>
+    <row r="4240"/>
+    <row r="4241"/>
+    <row r="4242"/>
+    <row r="4243"/>
+    <row r="4244"/>
+    <row r="4245"/>
+    <row r="4246"/>
+    <row r="4247"/>
+    <row r="4248"/>
+    <row r="4249"/>
+    <row r="4250"/>
+    <row r="4251"/>
+    <row r="4252"/>
+    <row r="4253"/>
+    <row r="4254"/>
+    <row r="4255"/>
+    <row r="4256"/>
+    <row r="4257"/>
+    <row r="4258"/>
+    <row r="4259"/>
+    <row r="4260"/>
+    <row r="4261"/>
+    <row r="4262"/>
+    <row r="4263"/>
+    <row r="4264"/>
+    <row r="4265"/>
+    <row r="4266"/>
+    <row r="4267"/>
+    <row r="4268"/>
+    <row r="4269"/>
+    <row r="4270"/>
+    <row r="4271"/>
+    <row r="4272"/>
+    <row r="4273"/>
+    <row r="4274"/>
+    <row r="4275"/>
+    <row r="4276"/>
+    <row r="4277"/>
+    <row r="4278"/>
+    <row r="4279"/>
+    <row r="4280"/>
+    <row r="4281"/>
+    <row r="4282"/>
+    <row r="4283"/>
+    <row r="4284"/>
+    <row r="4285"/>
+    <row r="4286"/>
+    <row r="4287"/>
+    <row r="4288"/>
+    <row r="4289"/>
+    <row r="4290"/>
+    <row r="4291"/>
+    <row r="4292"/>
+    <row r="4293"/>
+    <row r="4294"/>
+    <row r="4295"/>
+    <row r="4296"/>
+    <row r="4297"/>
+    <row r="4298"/>
+    <row r="4299"/>
+    <row r="4300"/>
+    <row r="4301"/>
+    <row r="4302"/>
+    <row r="4303"/>
+    <row r="4304"/>
+    <row r="4305"/>
+    <row r="4306"/>
+    <row r="4307"/>
+    <row r="4308"/>
+    <row r="4309"/>
+    <row r="4310"/>
+    <row r="4311"/>
+    <row r="4312"/>
+    <row r="4313"/>
+    <row r="4314"/>
+    <row r="4315"/>
+    <row r="4316"/>
+    <row r="4317"/>
+    <row r="4318"/>
+    <row r="4319"/>
+    <row r="4320"/>
+    <row r="4321"/>
+    <row r="4322"/>
+    <row r="4323"/>
+    <row r="4324"/>
+    <row r="4325"/>
+    <row r="4326"/>
+    <row r="4327"/>
+    <row r="4328"/>
+    <row r="4329"/>
+    <row r="4330"/>
+    <row r="4331"/>
+    <row r="4332"/>
+    <row r="4333"/>
+    <row r="4334"/>
+    <row r="4335"/>
+    <row r="4336"/>
+    <row r="4337"/>
+    <row r="4338"/>
+    <row r="4339"/>
+    <row r="4340"/>
+    <row r="4341"/>
+    <row r="4342"/>
+    <row r="4343"/>
+    <row r="4344"/>
+    <row r="4345"/>
+    <row r="4346"/>
+    <row r="4347"/>
+    <row r="4348"/>
+    <row r="4349"/>
+    <row r="4350"/>
+    <row r="4351"/>
+    <row r="4352"/>
+    <row r="4353"/>
+    <row r="4354"/>
+    <row r="4355"/>
+    <row r="4356"/>
+    <row r="4357"/>
+    <row r="4358"/>
+    <row r="4359"/>
+    <row r="4360"/>
+    <row r="4361"/>
+    <row r="4362"/>
+    <row r="4363"/>
+    <row r="4364"/>
+    <row r="4365"/>
+    <row r="4366"/>
+    <row r="4367"/>
+    <row r="4368"/>
+    <row r="4369"/>
+    <row r="4370"/>
+    <row r="4371"/>
+    <row r="4372"/>
+    <row r="4373"/>
+    <row r="4374"/>
+    <row r="4375"/>
+    <row r="4376"/>
+    <row r="4377"/>
+    <row r="4378"/>
+    <row r="4379"/>
+    <row r="4380"/>
+    <row r="4381"/>
+    <row r="4382"/>
+    <row r="4383"/>
+    <row r="4384"/>
+    <row r="4385"/>
+    <row r="4386"/>
+    <row r="4387"/>
+    <row r="4388"/>
+    <row r="4389"/>
+    <row r="4390"/>
+    <row r="4391"/>
+    <row r="4392"/>
+    <row r="4393"/>
+    <row r="4394"/>
+    <row r="4395"/>
+    <row r="4396"/>
+    <row r="4397"/>
+    <row r="4398"/>
+    <row r="4399"/>
+    <row r="4400"/>
+    <row r="4401"/>
+    <row r="4402"/>
+    <row r="4403"/>
+    <row r="4404"/>
+    <row r="4405"/>
+    <row r="4406"/>
+    <row r="4407"/>
+    <row r="4408"/>
+    <row r="4409"/>
+    <row r="4410"/>
+    <row r="4411"/>
+    <row r="4412"/>
+    <row r="4413"/>
+    <row r="4414"/>
+    <row r="4415"/>
+    <row r="4416"/>
+    <row r="4417"/>
+    <row r="4418"/>
+    <row r="4419"/>
+    <row r="4420"/>
+    <row r="4421"/>
+    <row r="4422"/>
+    <row r="4423"/>
+    <row r="4424"/>
+    <row r="4425"/>
+    <row r="4426"/>
+    <row r="4427"/>
+    <row r="4428"/>
+    <row r="4429"/>
+    <row r="4430"/>
+    <row r="4431"/>
+    <row r="4432"/>
+    <row r="4433"/>
+    <row r="4434"/>
+    <row r="4435"/>
+    <row r="4436"/>
+    <row r="4437"/>
+    <row r="4438"/>
+    <row r="4439"/>
+    <row r="4440"/>
+    <row r="4441"/>
+    <row r="4442"/>
+    <row r="4443"/>
+    <row r="4444"/>
+    <row r="4445"/>
+    <row r="4446"/>
+    <row r="4447"/>
+    <row r="4448"/>
+    <row r="4449"/>
+    <row r="4450"/>
+    <row r="4451"/>
+    <row r="4452"/>
+    <row r="4453"/>
+    <row r="4454"/>
+    <row r="4455"/>
+    <row r="4456"/>
+    <row r="4457"/>
+    <row r="4458"/>
+    <row r="4459"/>
+    <row r="4460"/>
+    <row r="4461"/>
+    <row r="4462"/>
+    <row r="4463"/>
+    <row r="4464"/>
+    <row r="4465"/>
+    <row r="4466"/>
+    <row r="4467"/>
+    <row r="4468"/>
+    <row r="4469"/>
+    <row r="4470"/>
+    <row r="4471"/>
+    <row r="4472"/>
+    <row r="4473"/>
+    <row r="4474"/>
+    <row r="4475"/>
+    <row r="4476"/>
+    <row r="4477"/>
+    <row r="4478"/>
+    <row r="4479"/>
+    <row r="4480"/>
+    <row r="4481"/>
+    <row r="4482"/>
+    <row r="4483"/>
+    <row r="4484"/>
+    <row r="4485"/>
+    <row r="4486"/>
+    <row r="4487"/>
+    <row r="4488"/>
+    <row r="4489"/>
+    <row r="4490"/>
+    <row r="4491"/>
+    <row r="4492"/>
+    <row r="4493"/>
+    <row r="4494"/>
+    <row r="4495"/>
+    <row r="4496"/>
+    <row r="4497"/>
+    <row r="4498"/>
+    <row r="4499"/>
+    <row r="4500"/>
+    <row r="4501"/>
+    <row r="4502"/>
+    <row r="4503"/>
+    <row r="4504"/>
+    <row r="4505"/>
+    <row r="4506"/>
+    <row r="4507"/>
+    <row r="4508"/>
+    <row r="4509"/>
+    <row r="4510"/>
+    <row r="4511"/>
+    <row r="4512"/>
+    <row r="4513"/>
+    <row r="4514"/>
+    <row r="4515"/>
+    <row r="4516"/>
+    <row r="4517"/>
+    <row r="4518"/>
+    <row r="4519"/>
+    <row r="4520"/>
+    <row r="4521"/>
+    <row r="4522"/>
+    <row r="4523"/>
+    <row r="4524"/>
+    <row r="4525"/>
+    <row r="4526"/>
+    <row r="4527"/>
+    <row r="4528"/>
+    <row r="4529"/>
+    <row r="4530"/>
+    <row r="4531"/>
+    <row r="4532"/>
+    <row r="4533"/>
+    <row r="4534"/>
+    <row r="4535"/>
+    <row r="4536"/>
+    <row r="4537"/>
+    <row r="4538"/>
+    <row r="4539"/>
+    <row r="4540"/>
+    <row r="4541"/>
+    <row r="4542"/>
+    <row r="4543"/>
+    <row r="4544"/>
+    <row r="4545"/>
+    <row r="4546"/>
+    <row r="4547"/>
+    <row r="4548"/>
+    <row r="4549"/>
+    <row r="4550"/>
+    <row r="4551"/>
+    <row r="4552"/>
+    <row r="4553"/>
+    <row r="4554"/>
+    <row r="4555"/>
+    <row r="4556"/>
+    <row r="4557"/>
+    <row r="4558"/>
+    <row r="4559"/>
+    <row r="4560"/>
+    <row r="4561"/>
+    <row r="4562"/>
+    <row r="4563"/>
+    <row r="4564"/>
+    <row r="4565"/>
+    <row r="4566"/>
+    <row r="4567"/>
+    <row r="4568"/>
+    <row r="4569"/>
+    <row r="4570"/>
+    <row r="4571"/>
+    <row r="4572"/>
+    <row r="4573"/>
+    <row r="4574"/>
+    <row r="4575"/>
+    <row r="4576"/>
+    <row r="4577"/>
+    <row r="4578"/>
+    <row r="4579"/>
+    <row r="4580"/>
+    <row r="4581"/>
+    <row r="4582"/>
+    <row r="4583"/>
+    <row r="4584"/>
+    <row r="4585"/>
+    <row r="4586"/>
+    <row r="4587"/>
+    <row r="4588"/>
+    <row r="4589"/>
+    <row r="4590"/>
+    <row r="4591"/>
+    <row r="4592"/>
+    <row r="4593"/>
+    <row r="4594"/>
+    <row r="4595"/>
+    <row r="4596"/>
+    <row r="4597"/>
+    <row r="4598"/>
+    <row r="4599"/>
+    <row r="4600"/>
+    <row r="4601"/>
+    <row r="4602"/>
+    <row r="4603"/>
+    <row r="4604"/>
+    <row r="4605"/>
+    <row r="4606"/>
+    <row r="4607"/>
+    <row r="4608"/>
+    <row r="4609"/>
+    <row r="4610"/>
+    <row r="4611"/>
+    <row r="4612"/>
+    <row r="4613"/>
+    <row r="4614"/>
+    <row r="4615"/>
+    <row r="4616"/>
+    <row r="4617"/>
+    <row r="4618"/>
+    <row r="4619"/>
+    <row r="4620"/>
+    <row r="4621"/>
+    <row r="4622"/>
+    <row r="4623"/>
+    <row r="4624"/>
+    <row r="4625"/>
+    <row r="4626"/>
+    <row r="4627"/>
+    <row r="4628"/>
+    <row r="4629"/>
+    <row r="4630"/>
+    <row r="4631"/>
+    <row r="4632"/>
+    <row r="4633"/>
+    <row r="4634"/>
+    <row r="4635"/>
+    <row r="4636"/>
+    <row r="4637"/>
+    <row r="4638"/>
+    <row r="4639"/>
+    <row r="4640"/>
+    <row r="4641"/>
+    <row r="4642"/>
+    <row r="4643"/>
+    <row r="4644"/>
+    <row r="4645"/>
+    <row r="4646"/>
+    <row r="4647"/>
+    <row r="4648"/>
+    <row r="4649"/>
+    <row r="4650"/>
+    <row r="4651"/>
+    <row r="4652"/>
+    <row r="4653"/>
+    <row r="4654"/>
+    <row r="4655"/>
+    <row r="4656"/>
+    <row r="4657"/>
+    <row r="4658"/>
+    <row r="4659"/>
+    <row r="4660"/>
+    <row r="4661"/>
+    <row r="4662"/>
+    <row r="4663"/>
+    <row r="4664"/>
+    <row r="4665"/>
+    <row r="4666"/>
+    <row r="4667"/>
+    <row r="4668"/>
+    <row r="4669"/>
+    <row r="4670"/>
+    <row r="4671"/>
+    <row r="4672"/>
+    <row r="4673"/>
+    <row r="4674"/>
+    <row r="4675"/>
+    <row r="4676"/>
+    <row r="4677"/>
+    <row r="4678"/>
+    <row r="4679"/>
+    <row r="4680"/>
+    <row r="4681"/>
+    <row r="4682"/>
+    <row r="4683"/>
+    <row r="4684"/>
+    <row r="4685"/>
+    <row r="4686"/>
+    <row r="4687"/>
+    <row r="4688"/>
+    <row r="4689"/>
+    <row r="4690"/>
+    <row r="4691"/>
+    <row r="4692"/>
+    <row r="4693"/>
+    <row r="4694"/>
+    <row r="4695"/>
+    <row r="4696"/>
+    <row r="4697"/>
+    <row r="4698"/>
+    <row r="4699"/>
+    <row r="4700"/>
+    <row r="4701"/>
+    <row r="4702"/>
+    <row r="4703"/>
+    <row r="4704"/>
+    <row r="4705"/>
+    <row r="4706"/>
+    <row r="4707"/>
+    <row r="4708"/>
+    <row r="4709"/>
+    <row r="4710"/>
+    <row r="4711"/>
+    <row r="4712"/>
+    <row r="4713"/>
+    <row r="4714"/>
+    <row r="4715"/>
+    <row r="4716"/>
+    <row r="4717"/>
+    <row r="4718"/>
+    <row r="4719"/>
+    <row r="4720"/>
+    <row r="4721"/>
+    <row r="4722"/>
+    <row r="4723"/>
+    <row r="4724"/>
+    <row r="4725"/>
+    <row r="4726"/>
+    <row r="4727"/>
+    <row r="4728"/>
+    <row r="4729"/>
+    <row r="4730"/>
+    <row r="4731"/>
+    <row r="4732"/>
+    <row r="4733"/>
+    <row r="4734"/>
+    <row r="4735"/>
+    <row r="4736"/>
+    <row r="4737"/>
+    <row r="4738"/>
+    <row r="4739"/>
+    <row r="4740"/>
+    <row r="4741"/>
+    <row r="4742"/>
+    <row r="4743"/>
+    <row r="4744"/>
+    <row r="4745"/>
+    <row r="4746"/>
+    <row r="4747"/>
+    <row r="4748"/>
+    <row r="4749"/>
+    <row r="4750"/>
+    <row r="4751"/>
+    <row r="4752"/>
+    <row r="4753"/>
+    <row r="4754"/>
+    <row r="4755"/>
+    <row r="4756"/>
+    <row r="4757"/>
+    <row r="4758"/>
+    <row r="4759"/>
+    <row r="4760"/>
+    <row r="4761"/>
+    <row r="4762"/>
+    <row r="4763"/>
+    <row r="4764"/>
+    <row r="4765"/>
+    <row r="4766"/>
+    <row r="4767"/>
+    <row r="4768"/>
+    <row r="4769"/>
+    <row r="4770"/>
+    <row r="4771"/>
+    <row r="4772"/>
+    <row r="4773"/>
+    <row r="4774"/>
+    <row r="4775"/>
+    <row r="4776"/>
+    <row r="4777"/>
+    <row r="4778"/>
+    <row r="4779"/>
+    <row r="4780"/>
+    <row r="4781"/>
+    <row r="4782"/>
+    <row r="4783"/>
+    <row r="4784"/>
+    <row r="4785"/>
+    <row r="4786"/>
+    <row r="4787"/>
+    <row r="4788"/>
+    <row r="4789"/>
+    <row r="4790"/>
+    <row r="4791"/>
+    <row r="4792"/>
+    <row r="4793"/>
+    <row r="4794"/>
+    <row r="4795"/>
+    <row r="4796"/>
+    <row r="4797"/>
+    <row r="4798"/>
+    <row r="4799"/>
+    <row r="4800"/>
+    <row r="4801"/>
+    <row r="4802"/>
+    <row r="4803"/>
+    <row r="4804"/>
+    <row r="4805"/>
+    <row r="4806"/>
+    <row r="4807"/>
+    <row r="4808"/>
+    <row r="4809"/>
+    <row r="4810"/>
+    <row r="4811"/>
+    <row r="4812"/>
+    <row r="4813"/>
+    <row r="4814"/>
+    <row r="4815"/>
+    <row r="4816"/>
+    <row r="4817"/>
+    <row r="4818"/>
+    <row r="4819"/>
+    <row r="4820"/>
+    <row r="4821"/>
+    <row r="4822"/>
+    <row r="4823"/>
+    <row r="4824"/>
+    <row r="4825"/>
+    <row r="4826"/>
+    <row r="4827"/>
+    <row r="4828"/>
+    <row r="4829"/>
+    <row r="4830"/>
+    <row r="4831"/>
+    <row r="4832"/>
+    <row r="4833"/>
+    <row r="4834"/>
+    <row r="4835"/>
+    <row r="4836"/>
+    <row r="4837"/>
+    <row r="4838"/>
+    <row r="4839"/>
+    <row r="4840"/>
+    <row r="4841"/>
+    <row r="4842"/>
+    <row r="4843"/>
+    <row r="4844"/>
+    <row r="4845"/>
+    <row r="4846"/>
+    <row r="4847"/>
+    <row r="4848"/>
+    <row r="4849"/>
+    <row r="4850"/>
+    <row r="4851"/>
+    <row r="4852"/>
+    <row r="4853"/>
+    <row r="4854"/>
+    <row r="4855"/>
+    <row r="4856"/>
+    <row r="4857"/>
+    <row r="4858"/>
+    <row r="4859"/>
+    <row r="4860"/>
+    <row r="4861"/>
+    <row r="4862"/>
+    <row r="4863"/>
+    <row r="4864"/>
+    <row r="4865"/>
+    <row r="4866"/>
+    <row r="4867"/>
+    <row r="4868"/>
+    <row r="4869"/>
+    <row r="4870"/>
+    <row r="4871"/>
+    <row r="4872"/>
+    <row r="4873"/>
+    <row r="4874"/>
+    <row r="4875"/>
+    <row r="4876"/>
+    <row r="4877"/>
+    <row r="4878"/>
+    <row r="4879"/>
+    <row r="4880"/>
+    <row r="4881"/>
+    <row r="4882"/>
+    <row r="4883"/>
+    <row r="4884"/>
+    <row r="4885"/>
+    <row r="4886"/>
+    <row r="4887"/>
+    <row r="4888"/>
+    <row r="4889"/>
+    <row r="4890"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>